--- a/research/traditional_assets/database/data/panama/panama_air_transport.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_air_transport.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1042233048242259</v>
+        <v>0.1039964965621653</v>
       </c>
       <c r="C2">
-        <v>5424.659689827138</v>
+        <v>5389.694595548175</v>
       </c>
       <c r="D2">
-        <v>5149.459689827138</v>
+        <v>5169.528595548175</v>
       </c>
       <c r="E2">
-        <v>-1858.8</v>
+        <v>-1803.766</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>55.034</v>
       </c>
       <c r="G2">
         <v>275.2</v>
@@ -1457,28 +1457,28 @@
         <v>681.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.7682102</v>
       </c>
       <c r="N2">
-        <v>681.7</v>
+        <v>678.9317898</v>
       </c>
       <c r="O2">
-        <v>170.425</v>
+        <v>169.73294745</v>
       </c>
       <c r="P2">
-        <v>511.275</v>
+        <v>509.1988423500001</v>
       </c>
       <c r="Q2">
-        <v>837.175</v>
+        <v>835.09884235</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1042233048242259</v>
+        <v>0.1046659056183488</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8103113482567638</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>246.2602009052636</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1039964965621653</v>
+        <v>0.1037696883001048</v>
       </c>
       <c r="C3">
-        <v>5389.694595548175</v>
+        <v>5354.886541741961</v>
       </c>
       <c r="D3">
-        <v>5169.528595548175</v>
+        <v>5189.754541741961</v>
       </c>
       <c r="E3">
-        <v>-1803.766</v>
+        <v>-1748.732</v>
       </c>
       <c r="F3">
-        <v>55.034</v>
+        <v>110.068</v>
       </c>
       <c r="G3">
         <v>275.2</v>
@@ -1539,28 +1539,28 @@
         <v>681.7</v>
       </c>
       <c r="M3">
-        <v>2.7682102</v>
+        <v>5.5364204</v>
       </c>
       <c r="N3">
-        <v>678.9317898</v>
+        <v>676.1635796</v>
       </c>
       <c r="O3">
-        <v>169.73294745</v>
+        <v>169.0408949</v>
       </c>
       <c r="P3">
-        <v>509.1988423500001</v>
+        <v>507.1226847</v>
       </c>
       <c r="Q3">
-        <v>835.09884235</v>
+        <v>833.0226847</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1046659056183488</v>
+        <v>0.1051175390817396</v>
       </c>
       <c r="T3">
-        <v>0.8103113482567638</v>
+        <v>0.8165282528774234</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>246.2602009052636</v>
+        <v>123.1301004526318</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1037696883001048</v>
+        <v>0.1035428800380442</v>
       </c>
       <c r="C4">
-        <v>5354.886541741961</v>
+        <v>5320.237378926356</v>
       </c>
       <c r="D4">
-        <v>5189.754541741961</v>
+        <v>5210.139378926356</v>
       </c>
       <c r="E4">
-        <v>-1748.732</v>
+        <v>-1693.698</v>
       </c>
       <c r="F4">
-        <v>110.068</v>
+        <v>165.102</v>
       </c>
       <c r="G4">
         <v>275.2</v>
@@ -1621,28 +1621,28 @@
         <v>681.7</v>
       </c>
       <c r="M4">
-        <v>5.5364204</v>
+        <v>8.304630599999998</v>
       </c>
       <c r="N4">
-        <v>676.1635796</v>
+        <v>673.3953694</v>
       </c>
       <c r="O4">
-        <v>169.0408949</v>
+        <v>168.34884235</v>
       </c>
       <c r="P4">
-        <v>507.1226847</v>
+        <v>505.04652705</v>
       </c>
       <c r="Q4">
-        <v>833.0226847</v>
+        <v>830.94652705</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1051175390817396</v>
+        <v>0.1055784845753033</v>
       </c>
       <c r="T4">
-        <v>0.8165282528774234</v>
+        <v>0.8228733410985087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.1301004526318</v>
+        <v>82.08673363508791</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1035428800380442</v>
+        <v>0.1033160717759836</v>
       </c>
       <c r="C5">
-        <v>5320.237378926356</v>
+        <v>5285.748986808448</v>
       </c>
       <c r="D5">
-        <v>5210.139378926356</v>
+        <v>5230.684986808448</v>
       </c>
       <c r="E5">
-        <v>-1693.698</v>
+        <v>-1638.664</v>
       </c>
       <c r="F5">
-        <v>165.102</v>
+        <v>220.136</v>
       </c>
       <c r="G5">
         <v>275.2</v>
@@ -1703,28 +1703,28 @@
         <v>681.7</v>
       </c>
       <c r="M5">
-        <v>8.304630599999998</v>
+        <v>11.0728408</v>
       </c>
       <c r="N5">
-        <v>673.3953694</v>
+        <v>670.6271592000001</v>
       </c>
       <c r="O5">
-        <v>168.34884235</v>
+        <v>167.6567898</v>
       </c>
       <c r="P5">
-        <v>505.04652705</v>
+        <v>502.9703694</v>
       </c>
       <c r="Q5">
-        <v>830.94652705</v>
+        <v>828.8703694000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1055784845753033</v>
+        <v>0.106049033099983</v>
       </c>
       <c r="T5">
-        <v>0.8228733410985087</v>
+        <v>0.8293506186575337</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.08673363508791</v>
+        <v>61.56505022631591</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1033160717759836</v>
+        <v>0.1030892635139231</v>
       </c>
       <c r="C6">
-        <v>5285.748986808448</v>
+        <v>5251.423274862385</v>
       </c>
       <c r="D6">
-        <v>5230.684986808448</v>
+        <v>5251.393274862386</v>
       </c>
       <c r="E6">
-        <v>-1638.664</v>
+        <v>-1583.63</v>
       </c>
       <c r="F6">
-        <v>220.136</v>
+        <v>275.17</v>
       </c>
       <c r="G6">
         <v>275.2</v>
@@ -1785,28 +1785,28 @@
         <v>681.7</v>
       </c>
       <c r="M6">
-        <v>11.0728408</v>
+        <v>13.841051</v>
       </c>
       <c r="N6">
-        <v>670.6271592000001</v>
+        <v>667.8589490000001</v>
       </c>
       <c r="O6">
-        <v>167.6567898</v>
+        <v>166.96473725</v>
       </c>
       <c r="P6">
-        <v>502.9703694</v>
+        <v>500.8942117500001</v>
       </c>
       <c r="Q6">
-        <v>828.8703694000001</v>
+        <v>826.79421175</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.106049033099983</v>
+        <v>0.1065294879093927</v>
       </c>
       <c r="T6">
-        <v>0.8293506186575337</v>
+        <v>0.8359642599546432</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.56505022631591</v>
+        <v>49.25204018105273</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1030892635139231</v>
+        <v>0.1028624552518625</v>
       </c>
       <c r="C7">
-        <v>5251.423274862385</v>
+        <v>5217.262182920952</v>
       </c>
       <c r="D7">
-        <v>5251.393274862386</v>
+        <v>5272.266182920952</v>
       </c>
       <c r="E7">
-        <v>-1583.63</v>
+        <v>-1528.596</v>
       </c>
       <c r="F7">
-        <v>275.17</v>
+        <v>330.204</v>
       </c>
       <c r="G7">
         <v>275.2</v>
@@ -1867,28 +1867,28 @@
         <v>681.7</v>
       </c>
       <c r="M7">
-        <v>13.841051</v>
+        <v>16.6092612</v>
       </c>
       <c r="N7">
-        <v>667.8589490000001</v>
+        <v>665.0907388000001</v>
       </c>
       <c r="O7">
-        <v>166.96473725</v>
+        <v>166.2726847</v>
       </c>
       <c r="P7">
-        <v>500.8942117500001</v>
+        <v>498.8180541</v>
       </c>
       <c r="Q7">
-        <v>826.79421175</v>
+        <v>824.7180541</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1065294879093927</v>
+        <v>0.1070201651615559</v>
       </c>
       <c r="T7">
-        <v>0.8359642599546432</v>
+        <v>0.8427186170240316</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.25204018105273</v>
+        <v>41.04336681754394</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1028624552518625</v>
+        <v>0.1026356469898019</v>
       </c>
       <c r="C8">
-        <v>5217.262182920952</v>
+        <v>5183.267681781297</v>
       </c>
       <c r="D8">
-        <v>5272.266182920952</v>
+        <v>5293.305681781298</v>
       </c>
       <c r="E8">
-        <v>-1528.596</v>
+        <v>-1473.562</v>
       </c>
       <c r="F8">
-        <v>330.204</v>
+        <v>385.2379999999999</v>
       </c>
       <c r="G8">
         <v>275.2</v>
@@ -1949,28 +1949,28 @@
         <v>681.7</v>
       </c>
       <c r="M8">
-        <v>16.6092612</v>
+        <v>19.3774714</v>
       </c>
       <c r="N8">
-        <v>665.0907388000001</v>
+        <v>662.3225286000001</v>
       </c>
       <c r="O8">
-        <v>166.2726847</v>
+        <v>165.58063215</v>
       </c>
       <c r="P8">
-        <v>498.8180541</v>
+        <v>496.74189645</v>
       </c>
       <c r="Q8">
-        <v>824.7180541</v>
+        <v>822.64189645</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1070201651615559</v>
+        <v>0.1075213946126903</v>
       </c>
       <c r="T8">
-        <v>0.8427186170240316</v>
+        <v>0.8496182290841595</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.04336681754395</v>
+        <v>35.18002870075195</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1026356469898019</v>
+        <v>0.1024088387277414</v>
       </c>
       <c r="C9">
-        <v>5183.267681781298</v>
+        <v>5149.441773825264</v>
       </c>
       <c r="D9">
-        <v>5293.305681781299</v>
+        <v>5314.513773825264</v>
       </c>
       <c r="E9">
-        <v>-1473.562</v>
+        <v>-1418.528</v>
       </c>
       <c r="F9">
-        <v>385.238</v>
+        <v>440.272</v>
       </c>
       <c r="G9">
         <v>275.2</v>
@@ -2031,28 +2031,28 @@
         <v>681.7</v>
       </c>
       <c r="M9">
-        <v>19.3774714</v>
+        <v>22.1456816</v>
       </c>
       <c r="N9">
-        <v>662.3225286000001</v>
+        <v>659.5543184000001</v>
       </c>
       <c r="O9">
-        <v>165.58063215</v>
+        <v>164.8885796</v>
       </c>
       <c r="P9">
-        <v>496.74189645</v>
+        <v>494.6657388</v>
       </c>
       <c r="Q9">
-        <v>822.64189645</v>
+        <v>820.5657388</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1075213946126903</v>
+        <v>0.1080335203562406</v>
       </c>
       <c r="T9">
-        <v>0.8496182290841595</v>
+        <v>0.8566678327108121</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.18002870075195</v>
+        <v>30.78252511315796</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1024088387277414</v>
+        <v>0.1021820304656808</v>
       </c>
       <c r="C10">
-        <v>5149.441773825264</v>
+        <v>5115.786493654661</v>
       </c>
       <c r="D10">
-        <v>5314.513773825264</v>
+        <v>5335.892493654661</v>
       </c>
       <c r="E10">
-        <v>-1418.528</v>
+        <v>-1363.494</v>
       </c>
       <c r="F10">
-        <v>440.272</v>
+        <v>495.3059999999999</v>
       </c>
       <c r="G10">
         <v>275.2</v>
@@ -2113,28 +2113,28 @@
         <v>681.7</v>
       </c>
       <c r="M10">
-        <v>22.1456816</v>
+        <v>24.91389179999999</v>
       </c>
       <c r="N10">
-        <v>659.5543184000001</v>
+        <v>656.7861082000001</v>
       </c>
       <c r="O10">
-        <v>164.8885796</v>
+        <v>164.19652705</v>
       </c>
       <c r="P10">
-        <v>494.6657388</v>
+        <v>492.5895811500001</v>
       </c>
       <c r="Q10">
-        <v>820.5657388</v>
+        <v>818.48958115</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1080335203562406</v>
+        <v>0.1085569016106382</v>
       </c>
       <c r="T10">
-        <v>0.8566678327108121</v>
+        <v>0.8638723726809074</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.78252511315796</v>
+        <v>27.3622445450293</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1021820304656808</v>
+        <v>0.1019552222036203</v>
       </c>
       <c r="C11">
-        <v>5115.786493654661</v>
+        <v>5082.303908741925</v>
       </c>
       <c r="D11">
-        <v>5335.892493654661</v>
+        <v>5357.443908741925</v>
       </c>
       <c r="E11">
-        <v>-1363.494</v>
+        <v>-1308.46</v>
       </c>
       <c r="F11">
-        <v>495.3059999999999</v>
+        <v>550.3399999999999</v>
       </c>
       <c r="G11">
         <v>275.2</v>
@@ -2195,28 +2195,28 @@
         <v>681.7</v>
       </c>
       <c r="M11">
-        <v>24.91389179999999</v>
+        <v>27.68210199999999</v>
       </c>
       <c r="N11">
-        <v>656.7861082000001</v>
+        <v>654.0178980000001</v>
       </c>
       <c r="O11">
-        <v>164.19652705</v>
+        <v>163.5044745</v>
       </c>
       <c r="P11">
-        <v>492.5895811500001</v>
+        <v>490.5134235</v>
       </c>
       <c r="Q11">
-        <v>818.48958115</v>
+        <v>816.4134235</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1085569016106382</v>
+        <v>0.1090919135595781</v>
       </c>
       <c r="T11">
-        <v>0.8638723726809074</v>
+        <v>0.8712370135392272</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.3622445450293</v>
+        <v>24.62602009052637</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1019552222036203</v>
+        <v>0.1017284139415597</v>
       </c>
       <c r="C12">
-        <v>5082.303908741925</v>
+        <v>5048.996120096649</v>
       </c>
       <c r="D12">
-        <v>5357.443908741925</v>
+        <v>5379.170120096649</v>
       </c>
       <c r="E12">
-        <v>-1308.46</v>
+        <v>-1253.426</v>
       </c>
       <c r="F12">
-        <v>550.34</v>
+        <v>605.3739999999999</v>
       </c>
       <c r="G12">
         <v>275.2</v>
@@ -2277,28 +2277,28 @@
         <v>681.7</v>
       </c>
       <c r="M12">
-        <v>27.682102</v>
+        <v>30.4503122</v>
       </c>
       <c r="N12">
-        <v>654.0178980000001</v>
+        <v>651.2496878000001</v>
       </c>
       <c r="O12">
-        <v>163.5044745</v>
+        <v>162.81242195</v>
       </c>
       <c r="P12">
-        <v>490.5134235</v>
+        <v>488.43726585</v>
       </c>
       <c r="Q12">
-        <v>816.4134235</v>
+        <v>814.33726585</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1090919135595781</v>
+        <v>0.1096389482489435</v>
       </c>
       <c r="T12">
-        <v>0.8712370135392272</v>
+        <v>0.8787671519449251</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.62602009052636</v>
+        <v>22.38729099138761</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1017284139415597</v>
+        <v>0.1015016056794991</v>
       </c>
       <c r="C13">
-        <v>5048.996120096649</v>
+        <v>5015.865262948349</v>
       </c>
       <c r="D13">
-        <v>5379.170120096649</v>
+        <v>5401.07326294835</v>
       </c>
       <c r="E13">
-        <v>-1253.426</v>
+        <v>-1198.392</v>
       </c>
       <c r="F13">
-        <v>605.3739999999999</v>
+        <v>660.4079999999999</v>
       </c>
       <c r="G13">
         <v>275.2</v>
@@ -2359,28 +2359,28 @@
         <v>681.7</v>
       </c>
       <c r="M13">
-        <v>30.4503122</v>
+        <v>33.21852239999999</v>
       </c>
       <c r="N13">
-        <v>651.2496878000001</v>
+        <v>648.4814776000001</v>
       </c>
       <c r="O13">
-        <v>162.81242195</v>
+        <v>162.1203694</v>
       </c>
       <c r="P13">
-        <v>488.43726585</v>
+        <v>486.3611082</v>
       </c>
       <c r="Q13">
-        <v>814.33726585</v>
+        <v>812.2611082000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1096389482489435</v>
+        <v>0.1101984155448854</v>
       </c>
       <c r="T13">
-        <v>0.8787671519449251</v>
+        <v>0.8864684298598431</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.38729099138761</v>
+        <v>20.52168340877198</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1015016056794991</v>
+        <v>0.1012747974174386</v>
       </c>
       <c r="C14">
-        <v>5015.865262948349</v>
+        <v>4982.913507446029</v>
       </c>
       <c r="D14">
-        <v>5401.07326294835</v>
+        <v>5423.155507446029</v>
       </c>
       <c r="E14">
-        <v>-1198.392</v>
+        <v>-1143.358</v>
       </c>
       <c r="F14">
-        <v>660.4079999999999</v>
+        <v>715.442</v>
       </c>
       <c r="G14">
         <v>275.2</v>
@@ -2441,28 +2441,28 @@
         <v>681.7</v>
       </c>
       <c r="M14">
-        <v>33.21852239999999</v>
+        <v>35.9867326</v>
       </c>
       <c r="N14">
-        <v>648.4814776000001</v>
+        <v>645.7132674000001</v>
       </c>
       <c r="O14">
-        <v>162.1203694</v>
+        <v>161.42831685</v>
       </c>
       <c r="P14">
-        <v>486.3611082</v>
+        <v>484.2849505500001</v>
       </c>
       <c r="Q14">
-        <v>812.2611082000001</v>
+        <v>810.1849505500001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1101984155448854</v>
+        <v>0.1107707441579754</v>
       </c>
       <c r="T14">
-        <v>0.8864684298598431</v>
+        <v>0.8943467486463685</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.52168340877198</v>
+        <v>18.94309237732798</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1012747974174386</v>
+        <v>0.101047989155378</v>
       </c>
       <c r="C15">
-        <v>4982.913507446029</v>
+        <v>4950.143059374931</v>
       </c>
       <c r="D15">
-        <v>5423.155507446029</v>
+        <v>5445.419059374931</v>
       </c>
       <c r="E15">
-        <v>-1143.358</v>
+        <v>-1088.324</v>
       </c>
       <c r="F15">
-        <v>715.442</v>
+        <v>770.476</v>
       </c>
       <c r="G15">
         <v>275.2</v>
@@ -2523,28 +2523,28 @@
         <v>681.7</v>
       </c>
       <c r="M15">
-        <v>35.9867326</v>
+        <v>38.75494279999999</v>
       </c>
       <c r="N15">
-        <v>645.7132674000001</v>
+        <v>642.9450572000001</v>
       </c>
       <c r="O15">
-        <v>161.42831685</v>
+        <v>160.7362643</v>
       </c>
       <c r="P15">
-        <v>484.2849505500001</v>
+        <v>482.2087929</v>
       </c>
       <c r="Q15">
-        <v>810.1849505500001</v>
+        <v>808.1087929</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1107707441579754</v>
+        <v>0.1113563827388116</v>
       </c>
       <c r="T15">
-        <v>0.8943467486463685</v>
+        <v>0.9024082841488597</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.94309237732798</v>
+        <v>17.59001435037598</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.101047989155378</v>
+        <v>0.1008211808933174</v>
       </c>
       <c r="C16">
-        <v>4950.143059374931</v>
+        <v>4917.556160891034</v>
       </c>
       <c r="D16">
-        <v>5445.419059374931</v>
+        <v>5467.866160891034</v>
       </c>
       <c r="E16">
-        <v>-1088.324</v>
+        <v>-1033.29</v>
       </c>
       <c r="F16">
-        <v>770.476</v>
+        <v>825.5100000000001</v>
       </c>
       <c r="G16">
         <v>275.2</v>
@@ -2605,28 +2605,28 @@
         <v>681.7</v>
       </c>
       <c r="M16">
-        <v>38.75494279999999</v>
+        <v>41.523153</v>
       </c>
       <c r="N16">
-        <v>642.9450572000001</v>
+        <v>640.1768470000001</v>
       </c>
       <c r="O16">
-        <v>160.7362643</v>
+        <v>160.04421175</v>
       </c>
       <c r="P16">
-        <v>482.2087929</v>
+        <v>480.13263525</v>
       </c>
       <c r="Q16">
-        <v>808.1087929</v>
+        <v>806.03263525</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1113563827388116</v>
+        <v>0.1119558010509617</v>
       </c>
       <c r="T16">
-        <v>0.9024082841488597</v>
+        <v>0.9106595028396448</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.59001435037598</v>
+        <v>16.41734672701758</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1008211808933174</v>
+        <v>0.1005943726312568</v>
       </c>
       <c r="C17">
-        <v>4917.556160891034</v>
+        <v>4885.155091273818</v>
       </c>
       <c r="D17">
-        <v>5467.866160891034</v>
+        <v>5490.499091273819</v>
       </c>
       <c r="E17">
-        <v>-1033.29</v>
+        <v>-978.256</v>
       </c>
       <c r="F17">
-        <v>825.5099999999999</v>
+        <v>880.544</v>
       </c>
       <c r="G17">
         <v>275.2</v>
@@ -2687,28 +2687,28 @@
         <v>681.7</v>
       </c>
       <c r="M17">
-        <v>41.52315299999999</v>
+        <v>44.2913632</v>
       </c>
       <c r="N17">
-        <v>640.1768470000001</v>
+        <v>637.4086368000001</v>
       </c>
       <c r="O17">
-        <v>160.04421175</v>
+        <v>159.3521592</v>
       </c>
       <c r="P17">
-        <v>480.13263525</v>
+        <v>478.0564776000001</v>
       </c>
       <c r="Q17">
-        <v>806.03263525</v>
+        <v>803.9564776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1119558010509617</v>
+        <v>0.1125694912276867</v>
       </c>
       <c r="T17">
-        <v>0.9106595028396448</v>
+        <v>0.9191071791183056</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.41734672701758</v>
+        <v>15.39126255657898</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1005943726312568</v>
+        <v>0.1003675643691963</v>
       </c>
       <c r="C18">
-        <v>4885.155091273818</v>
+        <v>4852.942167697744</v>
       </c>
       <c r="D18">
-        <v>5490.499091273819</v>
+        <v>5513.320167697744</v>
       </c>
       <c r="E18">
-        <v>-978.256</v>
+        <v>-923.222</v>
       </c>
       <c r="F18">
-        <v>880.544</v>
+        <v>935.578</v>
       </c>
       <c r="G18">
         <v>275.2</v>
@@ -2769,28 +2769,28 @@
         <v>681.7</v>
       </c>
       <c r="M18">
-        <v>44.2913632</v>
+        <v>47.0595734</v>
       </c>
       <c r="N18">
-        <v>637.4086368000001</v>
+        <v>634.6404266000001</v>
       </c>
       <c r="O18">
-        <v>159.3521592</v>
+        <v>158.66010665</v>
       </c>
       <c r="P18">
-        <v>478.0564776000001</v>
+        <v>475.9803199500001</v>
       </c>
       <c r="Q18">
-        <v>803.9564776</v>
+        <v>801.8803199500001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1125694912276867</v>
+        <v>0.1131979691195136</v>
       </c>
       <c r="T18">
-        <v>0.9191071791183056</v>
+        <v>0.9277584138615127</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.39126255657898</v>
+        <v>14.48589417089786</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1003675643691963</v>
+        <v>0.1001407561071357</v>
       </c>
       <c r="C19">
-        <v>4852.942167697744</v>
+        <v>4820.919746023106</v>
       </c>
       <c r="D19">
-        <v>5513.320167697744</v>
+        <v>5536.331746023106</v>
       </c>
       <c r="E19">
-        <v>-923.222</v>
+        <v>-868.1879999999999</v>
       </c>
       <c r="F19">
-        <v>935.578</v>
+        <v>990.6120000000001</v>
       </c>
       <c r="G19">
         <v>275.2</v>
@@ -2851,28 +2851,28 @@
         <v>681.7</v>
       </c>
       <c r="M19">
-        <v>47.0595734</v>
+        <v>49.8277836</v>
       </c>
       <c r="N19">
-        <v>634.6404266000001</v>
+        <v>631.8722164000001</v>
       </c>
       <c r="O19">
-        <v>158.66010665</v>
+        <v>157.9680541</v>
       </c>
       <c r="P19">
-        <v>475.9803199500001</v>
+        <v>473.9041623000001</v>
       </c>
       <c r="Q19">
-        <v>801.8803199500001</v>
+        <v>799.8041623</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1131979691195136</v>
+        <v>0.1138417757404094</v>
       </c>
       <c r="T19">
-        <v>0.9277584138615127</v>
+        <v>0.9366206543301636</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.48589417089786</v>
+        <v>13.68112227251465</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1001407561071357</v>
+        <v>0.09991394784507519</v>
       </c>
       <c r="C20">
-        <v>4820.919746023106</v>
+        <v>4789.090221606761</v>
       </c>
       <c r="D20">
-        <v>5536.331746023106</v>
+        <v>5559.536221606761</v>
       </c>
       <c r="E20">
-        <v>-868.1880000000001</v>
+        <v>-813.154</v>
       </c>
       <c r="F20">
-        <v>990.6119999999999</v>
+        <v>1045.646</v>
       </c>
       <c r="G20">
         <v>275.2</v>
@@ -2933,28 +2933,28 @@
         <v>681.7</v>
       </c>
       <c r="M20">
-        <v>49.82778359999999</v>
+        <v>52.5959938</v>
       </c>
       <c r="N20">
-        <v>631.8722164000001</v>
+        <v>629.1040062000001</v>
       </c>
       <c r="O20">
-        <v>157.9680541</v>
+        <v>157.27600155</v>
       </c>
       <c r="P20">
-        <v>473.9041623000001</v>
+        <v>471.82800465</v>
       </c>
       <c r="Q20">
-        <v>799.8041623</v>
+        <v>797.72800465</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1138417757404094</v>
+        <v>0.1145014788210805</v>
       </c>
       <c r="T20">
-        <v>0.9366206543301636</v>
+        <v>0.9457017155511271</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.68112227251465</v>
+        <v>12.96106320554019</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09991394784507519</v>
+        <v>0.09991213958301461</v>
       </c>
       <c r="C21">
-        <v>4789.090221606761</v>
+        <v>4734.242004288825</v>
       </c>
       <c r="D21">
-        <v>5559.536221606761</v>
+        <v>5559.722004288826</v>
       </c>
       <c r="E21">
-        <v>-813.154</v>
+        <v>-758.1199999999999</v>
       </c>
       <c r="F21">
-        <v>1045.646</v>
+        <v>1100.68</v>
       </c>
       <c r="G21">
         <v>275.2</v>
@@ -3015,45 +3015,45 @@
         <v>681.7</v>
       </c>
       <c r="M21">
-        <v>52.5959938</v>
+        <v>57.015224</v>
       </c>
       <c r="N21">
-        <v>629.1040062000001</v>
+        <v>624.6847760000001</v>
       </c>
       <c r="O21">
-        <v>157.27600155</v>
+        <v>156.171194</v>
       </c>
       <c r="P21">
-        <v>471.82800465</v>
+        <v>468.513582</v>
       </c>
       <c r="Q21">
-        <v>797.72800465</v>
+        <v>794.413582</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1145014788210805</v>
+        <v>0.1151776744787683</v>
       </c>
       <c r="T21">
-        <v>0.9457017155511271</v>
+        <v>0.9550098033026145</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>12.96106320554019</v>
+        <v>11.95645570032313</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09991213958301461</v>
+        <v>0.09969658132095403</v>
       </c>
       <c r="C22">
-        <v>4734.242004288825</v>
+        <v>4701.443997433691</v>
       </c>
       <c r="D22">
-        <v>5559.722004288826</v>
+        <v>5581.957997433691</v>
       </c>
       <c r="E22">
-        <v>-758.1199999999999</v>
+        <v>-703.086</v>
       </c>
       <c r="F22">
-        <v>1100.68</v>
+        <v>1155.714</v>
       </c>
       <c r="G22">
         <v>275.2</v>
@@ -3097,28 +3097,28 @@
         <v>681.7</v>
       </c>
       <c r="M22">
-        <v>57.015224</v>
+        <v>59.8659852</v>
       </c>
       <c r="N22">
-        <v>624.6847760000001</v>
+        <v>621.8340148000001</v>
       </c>
       <c r="O22">
-        <v>156.171194</v>
+        <v>155.4585037</v>
       </c>
       <c r="P22">
-        <v>468.513582</v>
+        <v>466.3755111</v>
       </c>
       <c r="Q22">
-        <v>794.413582</v>
+        <v>792.2755111</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1151776744787683</v>
+        <v>0.1158709890138659</v>
       </c>
       <c r="T22">
-        <v>0.9550098033026145</v>
+        <v>0.9645535388452788</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.95645570032313</v>
+        <v>11.38710066697441</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09969658132095403</v>
+        <v>0.09948102305889346</v>
       </c>
       <c r="C23">
-        <v>4701.443997433691</v>
+        <v>4668.824569590817</v>
       </c>
       <c r="D23">
-        <v>5581.957997433691</v>
+        <v>5604.372569590817</v>
       </c>
       <c r="E23">
-        <v>-703.086</v>
+        <v>-648.0520000000001</v>
       </c>
       <c r="F23">
-        <v>1155.714</v>
+        <v>1210.748</v>
       </c>
       <c r="G23">
         <v>275.2</v>
@@ -3179,28 +3179,28 @@
         <v>681.7</v>
       </c>
       <c r="M23">
-        <v>59.8659852</v>
+        <v>62.71674639999999</v>
       </c>
       <c r="N23">
-        <v>621.8340148000001</v>
+        <v>618.9832536</v>
       </c>
       <c r="O23">
-        <v>155.4585037</v>
+        <v>154.7458134</v>
       </c>
       <c r="P23">
-        <v>466.3755111</v>
+        <v>464.2374402</v>
       </c>
       <c r="Q23">
-        <v>792.2755111</v>
+        <v>790.1374402</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1158709890138659</v>
+        <v>0.1165820808447352</v>
       </c>
       <c r="T23">
-        <v>0.9645535388452788</v>
+        <v>0.9743419855557037</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.38710066697441</v>
+        <v>10.86950518211194</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09948102305889346</v>
+        <v>0.09926546479683292</v>
       </c>
       <c r="C24">
-        <v>4668.824569590817</v>
+        <v>4636.385880706719</v>
       </c>
       <c r="D24">
-        <v>5604.372569590817</v>
+        <v>5626.967880706719</v>
       </c>
       <c r="E24">
-        <v>-648.0520000000001</v>
+        <v>-593.018</v>
       </c>
       <c r="F24">
-        <v>1210.748</v>
+        <v>1265.782</v>
       </c>
       <c r="G24">
         <v>275.2</v>
@@ -3261,28 +3261,28 @@
         <v>681.7</v>
       </c>
       <c r="M24">
-        <v>62.71674639999999</v>
+        <v>65.5675076</v>
       </c>
       <c r="N24">
-        <v>618.9832536</v>
+        <v>616.1324924</v>
       </c>
       <c r="O24">
-        <v>154.7458134</v>
+        <v>154.0331231</v>
       </c>
       <c r="P24">
-        <v>464.2374402</v>
+        <v>462.0993693</v>
       </c>
       <c r="Q24">
-        <v>790.1374402</v>
+        <v>787.9993693</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1165820808447352</v>
+        <v>0.1173116425932895</v>
       </c>
       <c r="T24">
-        <v>0.9743419855557037</v>
+        <v>0.9843846776352307</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.86950518211194</v>
+        <v>10.39691800028098</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09926546479683292</v>
+        <v>0.09904990653477234</v>
       </c>
       <c r="C25">
-        <v>4636.385880706719</v>
+        <v>4604.130125702206</v>
       </c>
       <c r="D25">
-        <v>5626.967880706719</v>
+        <v>5649.746125702206</v>
       </c>
       <c r="E25">
-        <v>-593.018</v>
+        <v>-537.9839999999999</v>
       </c>
       <c r="F25">
-        <v>1265.782</v>
+        <v>1320.816</v>
       </c>
       <c r="G25">
         <v>275.2</v>
@@ -3343,28 +3343,28 @@
         <v>681.7</v>
       </c>
       <c r="M25">
-        <v>65.5675076</v>
+        <v>68.41826880000001</v>
       </c>
       <c r="N25">
-        <v>616.1324924</v>
+        <v>613.2817312000001</v>
       </c>
       <c r="O25">
-        <v>154.0331231</v>
+        <v>153.3204328</v>
       </c>
       <c r="P25">
-        <v>462.0993693</v>
+        <v>459.9612984</v>
       </c>
       <c r="Q25">
-        <v>787.9993693</v>
+        <v>785.8612984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1173116425932895</v>
+        <v>0.1180604033352268</v>
       </c>
       <c r="T25">
-        <v>0.9843846776352307</v>
+        <v>0.9946916510852717</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.39691800028098</v>
+        <v>9.963713083602606</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09904990653477234</v>
+        <v>0.09915309827271178</v>
       </c>
       <c r="C26">
-        <v>4604.130125702206</v>
+        <v>4538.168791760927</v>
       </c>
       <c r="D26">
-        <v>5649.746125702206</v>
+        <v>5638.818791760928</v>
       </c>
       <c r="E26">
-        <v>-537.9840000000002</v>
+        <v>-482.95</v>
       </c>
       <c r="F26">
-        <v>1320.816</v>
+        <v>1375.85</v>
       </c>
       <c r="G26">
         <v>275.2</v>
@@ -3425,45 +3425,45 @@
         <v>681.7</v>
       </c>
       <c r="M26">
-        <v>68.41826879999999</v>
+        <v>73.607975</v>
       </c>
       <c r="N26">
-        <v>613.2817312000001</v>
+        <v>608.092025</v>
       </c>
       <c r="O26">
-        <v>153.3204328</v>
+        <v>152.02300625</v>
       </c>
       <c r="P26">
-        <v>459.9612984</v>
+        <v>456.0690187500001</v>
       </c>
       <c r="Q26">
-        <v>785.8612984</v>
+        <v>781.96901875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1180604033352268</v>
+        <v>0.1188291310302824</v>
       </c>
       <c r="T26">
-        <v>0.9946916510852717</v>
+        <v>1.005273477160647</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.963713083602608</v>
+        <v>9.261224751801691</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09915309827271178</v>
+        <v>0.09895029001065121</v>
       </c>
       <c r="C27">
-        <v>4538.168791760927</v>
+        <v>4504.651119122496</v>
       </c>
       <c r="D27">
-        <v>5638.818791760928</v>
+        <v>5660.335119122497</v>
       </c>
       <c r="E27">
-        <v>-482.95</v>
+        <v>-427.9159999999999</v>
       </c>
       <c r="F27">
-        <v>1375.85</v>
+        <v>1430.884</v>
       </c>
       <c r="G27">
         <v>275.2</v>
@@ -3507,28 +3507,28 @@
         <v>681.7</v>
       </c>
       <c r="M27">
-        <v>73.607975</v>
+        <v>76.552294</v>
       </c>
       <c r="N27">
-        <v>608.092025</v>
+        <v>605.1477060000001</v>
       </c>
       <c r="O27">
-        <v>152.02300625</v>
+        <v>151.2869265</v>
       </c>
       <c r="P27">
-        <v>456.0690187500001</v>
+        <v>453.8607795</v>
       </c>
       <c r="Q27">
-        <v>781.96901875</v>
+        <v>779.7607795</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1188291310302824</v>
+        <v>0.1196186351495287</v>
       </c>
       <c r="T27">
-        <v>1.005273477160647</v>
+        <v>1.016141298535357</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.261224751801691</v>
+        <v>8.905023799809317</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09895029001065121</v>
+        <v>0.09874748174859066</v>
       </c>
       <c r="C28">
-        <v>4504.651119122496</v>
+        <v>4471.298277324512</v>
       </c>
       <c r="D28">
-        <v>5660.335119122497</v>
+        <v>5682.016277324512</v>
       </c>
       <c r="E28">
-        <v>-427.9159999999999</v>
+        <v>-372.8820000000001</v>
       </c>
       <c r="F28">
-        <v>1430.884</v>
+        <v>1485.918</v>
       </c>
       <c r="G28">
         <v>275.2</v>
@@ -3589,28 +3589,28 @@
         <v>681.7</v>
       </c>
       <c r="M28">
-        <v>76.552294</v>
+        <v>79.496613</v>
       </c>
       <c r="N28">
-        <v>605.1477060000001</v>
+        <v>602.203387</v>
       </c>
       <c r="O28">
-        <v>151.2869265</v>
+        <v>150.55084675</v>
       </c>
       <c r="P28">
-        <v>453.8607795</v>
+        <v>451.65254025</v>
       </c>
       <c r="Q28">
-        <v>779.7607795</v>
+        <v>777.55254025</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1196186351495287</v>
+        <v>0.1204297695186173</v>
       </c>
       <c r="T28">
-        <v>1.016141298535357</v>
+        <v>1.02730686844088</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.905023799809317</v>
+        <v>8.575208103520083</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09874748174859066</v>
+        <v>0.09854467348653009</v>
       </c>
       <c r="C29">
-        <v>4471.298277324512</v>
+        <v>4438.112167737528</v>
       </c>
       <c r="D29">
-        <v>5682.016277324512</v>
+        <v>5703.864167737528</v>
       </c>
       <c r="E29">
-        <v>-372.8820000000001</v>
+        <v>-317.848</v>
       </c>
       <c r="F29">
-        <v>1485.918</v>
+        <v>1540.952</v>
       </c>
       <c r="G29">
         <v>275.2</v>
@@ -3671,28 +3671,28 @@
         <v>681.7</v>
       </c>
       <c r="M29">
-        <v>79.496613</v>
+        <v>82.440932</v>
       </c>
       <c r="N29">
-        <v>602.203387</v>
+        <v>599.2590680000001</v>
       </c>
       <c r="O29">
-        <v>150.55084675</v>
+        <v>149.814767</v>
       </c>
       <c r="P29">
-        <v>451.65254025</v>
+        <v>449.4443010000001</v>
       </c>
       <c r="Q29">
-        <v>777.55254025</v>
+        <v>775.3443010000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1204297695186173</v>
+        <v>0.1212634353979584</v>
       </c>
       <c r="T29">
-        <v>1.02730686844088</v>
+        <v>1.038782593066002</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.575208103520083</v>
+        <v>8.26895067125151</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09854467348653009</v>
+        <v>0.09834186522446953</v>
       </c>
       <c r="C30">
-        <v>4438.112167737528</v>
+        <v>4405.094721088773</v>
       </c>
       <c r="D30">
-        <v>5703.864167737528</v>
+        <v>5725.880721088773</v>
       </c>
       <c r="E30">
-        <v>-317.848</v>
+        <v>-262.8139999999999</v>
       </c>
       <c r="F30">
-        <v>1540.952</v>
+        <v>1595.986</v>
       </c>
       <c r="G30">
         <v>275.2</v>
@@ -3753,28 +3753,28 @@
         <v>681.7</v>
       </c>
       <c r="M30">
-        <v>82.440932</v>
+        <v>85.38525100000001</v>
       </c>
       <c r="N30">
-        <v>599.2590680000001</v>
+        <v>596.314749</v>
       </c>
       <c r="O30">
-        <v>149.814767</v>
+        <v>149.07868725</v>
       </c>
       <c r="P30">
-        <v>449.4443010000001</v>
+        <v>447.23606175</v>
       </c>
       <c r="Q30">
-        <v>775.3443010000001</v>
+        <v>773.13606175</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1212634353979584</v>
+        <v>0.1221205848231965</v>
       </c>
       <c r="T30">
-        <v>1.038782593066002</v>
+        <v>1.050581577539718</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.26895067125151</v>
+        <v>7.983814441208352</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09834186522446953</v>
+        <v>0.09813905696240896</v>
       </c>
       <c r="C31">
-        <v>4405.094721088773</v>
+        <v>4372.247898030921</v>
       </c>
       <c r="D31">
-        <v>5725.880721088773</v>
+        <v>5748.06789803092</v>
       </c>
       <c r="E31">
-        <v>-262.8140000000001</v>
+        <v>-207.7800000000002</v>
       </c>
       <c r="F31">
-        <v>1595.986</v>
+        <v>1651.02</v>
       </c>
       <c r="G31">
         <v>275.2</v>
@@ -3835,28 +3835,28 @@
         <v>681.7</v>
       </c>
       <c r="M31">
-        <v>85.385251</v>
+        <v>88.32956999999999</v>
       </c>
       <c r="N31">
-        <v>596.314749</v>
+        <v>593.3704300000001</v>
       </c>
       <c r="O31">
-        <v>149.07868725</v>
+        <v>148.3426075</v>
       </c>
       <c r="P31">
-        <v>447.23606175</v>
+        <v>445.0278225000001</v>
       </c>
       <c r="Q31">
-        <v>773.13606175</v>
+        <v>770.9278225</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1221205848231965</v>
+        <v>0.1230022242320128</v>
       </c>
       <c r="T31">
-        <v>1.050581577539718</v>
+        <v>1.062717675855541</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.983814441208354</v>
+        <v>7.717687293168076</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09813905696240896</v>
+        <v>0.09812224870034839</v>
       </c>
       <c r="C32">
-        <v>4372.247898030921</v>
+        <v>4319.060436243094</v>
       </c>
       <c r="D32">
-        <v>5748.06789803092</v>
+        <v>5749.914436243094</v>
       </c>
       <c r="E32">
-        <v>-207.7800000000002</v>
+        <v>-152.7460000000001</v>
       </c>
       <c r="F32">
-        <v>1651.02</v>
+        <v>1706.054</v>
       </c>
       <c r="G32">
         <v>275.2</v>
@@ -3917,45 +3917,45 @@
         <v>681.7</v>
       </c>
       <c r="M32">
-        <v>88.32956999999999</v>
+        <v>92.63873219999999</v>
       </c>
       <c r="N32">
-        <v>593.3704300000001</v>
+        <v>589.0612678</v>
       </c>
       <c r="O32">
-        <v>148.3426075</v>
+        <v>147.26531695</v>
       </c>
       <c r="P32">
-        <v>445.0278225000001</v>
+        <v>441.79595085</v>
       </c>
       <c r="Q32">
-        <v>770.9278225</v>
+        <v>767.6959508499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1230022242320128</v>
+        <v>0.123909418406302</v>
       </c>
       <c r="T32">
-        <v>1.062717675855541</v>
+        <v>1.07520554513704</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.717687293168076</v>
+        <v>7.358693106121762</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09812224870034839</v>
+        <v>0.09792544043828781</v>
       </c>
       <c r="C33">
-        <v>4319.060436243094</v>
+        <v>4285.736193660565</v>
       </c>
       <c r="D33">
-        <v>5749.914436243094</v>
+        <v>5771.624193660565</v>
       </c>
       <c r="E33">
-        <v>-152.7460000000001</v>
+        <v>-97.71199999999999</v>
       </c>
       <c r="F33">
-        <v>1706.054</v>
+        <v>1761.088</v>
       </c>
       <c r="G33">
         <v>275.2</v>
@@ -3999,28 +3999,28 @@
         <v>681.7</v>
       </c>
       <c r="M33">
-        <v>92.63873219999999</v>
+        <v>95.6270784</v>
       </c>
       <c r="N33">
-        <v>589.0612678</v>
+        <v>586.0729216000001</v>
       </c>
       <c r="O33">
-        <v>147.26531695</v>
+        <v>146.5182304</v>
       </c>
       <c r="P33">
-        <v>441.79595085</v>
+        <v>439.5546912000001</v>
       </c>
       <c r="Q33">
-        <v>767.6959508499999</v>
+        <v>765.4546912000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.123909418406302</v>
+        <v>0.124843294762188</v>
       </c>
       <c r="T33">
-        <v>1.07520554513704</v>
+        <v>1.088060704691524</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.358693106121762</v>
+        <v>7.128733946555457</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09792544043828781</v>
+        <v>0.09772863217622725</v>
       </c>
       <c r="C34">
-        <v>4285.736193660565</v>
+        <v>4252.576509990833</v>
       </c>
       <c r="D34">
-        <v>5771.624193660565</v>
+        <v>5793.498509990834</v>
       </c>
       <c r="E34">
-        <v>-97.71199999999999</v>
+        <v>-42.67799999999988</v>
       </c>
       <c r="F34">
-        <v>1761.088</v>
+        <v>1816.122</v>
       </c>
       <c r="G34">
         <v>275.2</v>
@@ -4081,28 +4081,28 @@
         <v>681.7</v>
       </c>
       <c r="M34">
-        <v>95.6270784</v>
+        <v>98.61542460000001</v>
       </c>
       <c r="N34">
-        <v>586.0729216000001</v>
+        <v>583.0845754000001</v>
       </c>
       <c r="O34">
-        <v>146.5182304</v>
+        <v>145.77114385</v>
       </c>
       <c r="P34">
-        <v>439.5546912000001</v>
+        <v>437.31343155</v>
       </c>
       <c r="Q34">
-        <v>765.4546912000001</v>
+        <v>763.21343155</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.124843294762188</v>
+        <v>0.1258050480242198</v>
       </c>
       <c r="T34">
-        <v>1.088060704691524</v>
+        <v>1.101299600352112</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.128733946555457</v>
+        <v>6.912711705750745</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09772863217622725</v>
+        <v>0.09753182391416669</v>
       </c>
       <c r="C35">
-        <v>4252.576509990833</v>
+        <v>4219.583263374932</v>
       </c>
       <c r="D35">
-        <v>5793.498509990834</v>
+        <v>5815.539263374932</v>
       </c>
       <c r="E35">
-        <v>-42.67799999999988</v>
+        <v>12.35599999999999</v>
       </c>
       <c r="F35">
-        <v>1816.122</v>
+        <v>1871.156</v>
       </c>
       <c r="G35">
         <v>275.2</v>
@@ -4163,28 +4163,28 @@
         <v>681.7</v>
       </c>
       <c r="M35">
-        <v>98.61542460000001</v>
+        <v>101.6037708</v>
       </c>
       <c r="N35">
-        <v>583.0845754000001</v>
+        <v>580.0962292</v>
       </c>
       <c r="O35">
-        <v>145.77114385</v>
+        <v>145.0240573</v>
       </c>
       <c r="P35">
-        <v>437.31343155</v>
+        <v>435.0721719000001</v>
       </c>
       <c r="Q35">
-        <v>763.21343155</v>
+        <v>760.9721719</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1258050480242198</v>
+        <v>0.126795945324495</v>
       </c>
       <c r="T35">
-        <v>1.101299600352112</v>
+        <v>1.114939674669081</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.912711705750745</v>
+        <v>6.709396655581607</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09753182391416669</v>
+        <v>0.09733501565210612</v>
       </c>
       <c r="C36">
-        <v>4219.583263374932</v>
+        <v>4186.758360643793</v>
       </c>
       <c r="D36">
-        <v>5815.539263374932</v>
+        <v>5837.748360643793</v>
       </c>
       <c r="E36">
-        <v>12.35599999999999</v>
+        <v>67.3900000000001</v>
       </c>
       <c r="F36">
-        <v>1871.156</v>
+        <v>1926.19</v>
       </c>
       <c r="G36">
         <v>275.2</v>
@@ -4245,28 +4245,28 @@
         <v>681.7</v>
       </c>
       <c r="M36">
-        <v>101.6037708</v>
+        <v>104.592117</v>
       </c>
       <c r="N36">
-        <v>580.0962292</v>
+        <v>577.107883</v>
       </c>
       <c r="O36">
-        <v>145.0240573</v>
+        <v>144.27697075</v>
       </c>
       <c r="P36">
-        <v>435.0721719000001</v>
+        <v>432.83091225</v>
       </c>
       <c r="Q36">
-        <v>760.9721719</v>
+        <v>758.73091225</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.126795945324495</v>
+        <v>0.127817331772471</v>
       </c>
       <c r="T36">
-        <v>1.114939674669081</v>
+        <v>1.128999443580419</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.709396655581607</v>
+        <v>6.517699608279274</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09733501565210612</v>
+        <v>0.09713820739004556</v>
       </c>
       <c r="C37">
-        <v>4186.758360643793</v>
+        <v>4154.10373786817</v>
       </c>
       <c r="D37">
-        <v>5837.748360643793</v>
+        <v>5860.127737868171</v>
       </c>
       <c r="E37">
-        <v>67.3900000000001</v>
+        <v>122.4240000000002</v>
       </c>
       <c r="F37">
-        <v>1926.19</v>
+        <v>1981.224</v>
       </c>
       <c r="G37">
         <v>275.2</v>
@@ -4327,28 +4327,28 @@
         <v>681.7</v>
       </c>
       <c r="M37">
-        <v>104.592117</v>
+        <v>107.5804632</v>
       </c>
       <c r="N37">
-        <v>577.107883</v>
+        <v>574.1195368</v>
       </c>
       <c r="O37">
-        <v>144.27697075</v>
+        <v>143.5298842</v>
       </c>
       <c r="P37">
-        <v>432.83091225</v>
+        <v>430.5896526</v>
       </c>
       <c r="Q37">
-        <v>758.73091225</v>
+        <v>756.4896526</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.127817331772471</v>
+        <v>0.1288706365469462</v>
       </c>
       <c r="T37">
-        <v>1.128999443580419</v>
+        <v>1.143498580270236</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.517699608279274</v>
+        <v>6.336652396938183</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09713820739004556</v>
+        <v>0.096941399127985</v>
       </c>
       <c r="C38">
-        <v>4154.10373786817</v>
+        <v>4121.621360921276</v>
       </c>
       <c r="D38">
-        <v>5860.127737868171</v>
+        <v>5882.679360921276</v>
       </c>
       <c r="E38">
-        <v>122.4239999999998</v>
+        <v>177.4579999999999</v>
       </c>
       <c r="F38">
-        <v>1981.224</v>
+        <v>2036.258</v>
       </c>
       <c r="G38">
         <v>275.2</v>
@@ -4409,28 +4409,28 @@
         <v>681.7</v>
       </c>
       <c r="M38">
-        <v>107.5804632</v>
+        <v>110.5688094</v>
       </c>
       <c r="N38">
-        <v>574.1195368000001</v>
+        <v>571.1311906000001</v>
       </c>
       <c r="O38">
-        <v>143.5298842</v>
+        <v>142.78279765</v>
       </c>
       <c r="P38">
-        <v>430.5896526000001</v>
+        <v>428.3483929500001</v>
       </c>
       <c r="Q38">
-        <v>756.4896526</v>
+        <v>754.24839295</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1288706365469462</v>
+        <v>0.1299573795682302</v>
       </c>
       <c r="T38">
-        <v>1.143498580270236</v>
+        <v>1.158458007013698</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.336652396938184</v>
+        <v>6.16539152134526</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.096941399127985</v>
+        <v>0.09702959086592444</v>
       </c>
       <c r="C39">
-        <v>4121.621360921276</v>
+        <v>4056.460328715652</v>
       </c>
       <c r="D39">
-        <v>5882.679360921276</v>
+        <v>5872.552328715652</v>
       </c>
       <c r="E39">
-        <v>177.4579999999999</v>
+        <v>232.492</v>
       </c>
       <c r="F39">
-        <v>2036.258</v>
+        <v>2091.292</v>
       </c>
       <c r="G39">
         <v>275.2</v>
@@ -4491,45 +4491,45 @@
         <v>681.7</v>
       </c>
       <c r="M39">
-        <v>110.5688094</v>
+        <v>115.6484476</v>
       </c>
       <c r="N39">
-        <v>571.1311906000001</v>
+        <v>566.0515524</v>
       </c>
       <c r="O39">
-        <v>142.78279765</v>
+        <v>141.5128881</v>
       </c>
       <c r="P39">
-        <v>428.3483929500001</v>
+        <v>424.5386643</v>
       </c>
       <c r="Q39">
-        <v>754.24839295</v>
+        <v>750.4386643</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1299573795682302</v>
+        <v>0.1310791788160072</v>
       </c>
       <c r="T39">
-        <v>1.158458007013698</v>
+        <v>1.173899995910175</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.16539152134526</v>
+        <v>5.89458841987949</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09702959086592444</v>
+        <v>0.09684028260386388</v>
       </c>
       <c r="C40">
-        <v>4056.460328715652</v>
+        <v>4023.207608491025</v>
       </c>
       <c r="D40">
-        <v>5872.552328715652</v>
+        <v>5894.333608491025</v>
       </c>
       <c r="E40">
-        <v>232.492</v>
+        <v>287.5260000000001</v>
       </c>
       <c r="F40">
-        <v>2091.292</v>
+        <v>2146.326</v>
       </c>
       <c r="G40">
         <v>275.2</v>
@@ -4573,28 +4573,28 @@
         <v>681.7</v>
       </c>
       <c r="M40">
-        <v>115.6484476</v>
+        <v>118.6918278</v>
       </c>
       <c r="N40">
-        <v>566.0515524</v>
+        <v>563.0081722</v>
       </c>
       <c r="O40">
-        <v>141.5128881</v>
+        <v>140.75204305</v>
       </c>
       <c r="P40">
-        <v>424.5386643</v>
+        <v>422.25612915</v>
       </c>
       <c r="Q40">
-        <v>750.4386643</v>
+        <v>748.15612915</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1310791788160072</v>
+        <v>0.1322377583669899</v>
       </c>
       <c r="T40">
-        <v>1.173899995910175</v>
+        <v>1.189848279524569</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.89458841987949</v>
+        <v>5.743445127062067</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09684028260386388</v>
+        <v>0.09665097434180331</v>
       </c>
       <c r="C41">
-        <v>4023.207608491025</v>
+        <v>3990.117063181357</v>
       </c>
       <c r="D41">
-        <v>5894.333608491025</v>
+        <v>5916.277063181357</v>
       </c>
       <c r="E41">
-        <v>287.5260000000001</v>
+        <v>342.5600000000002</v>
       </c>
       <c r="F41">
-        <v>2146.326</v>
+        <v>2201.36</v>
       </c>
       <c r="G41">
         <v>275.2</v>
@@ -4655,28 +4655,28 @@
         <v>681.7</v>
       </c>
       <c r="M41">
-        <v>118.6918278</v>
+        <v>121.735208</v>
       </c>
       <c r="N41">
-        <v>563.0081722</v>
+        <v>559.964792</v>
       </c>
       <c r="O41">
-        <v>140.75204305</v>
+        <v>139.991198</v>
       </c>
       <c r="P41">
-        <v>422.25612915</v>
+        <v>419.973594</v>
       </c>
       <c r="Q41">
-        <v>748.15612915</v>
+        <v>745.8735939999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1322377583669899</v>
+        <v>0.1334349572363388</v>
       </c>
       <c r="T41">
-        <v>1.189848279524569</v>
+        <v>1.206328172592776</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.743445127062067</v>
+        <v>5.599858998885515</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09665097434180331</v>
+        <v>0.09646166607974274</v>
       </c>
       <c r="C42">
-        <v>3990.117063181357</v>
+        <v>3957.190510791484</v>
       </c>
       <c r="D42">
-        <v>5916.277063181357</v>
+        <v>5938.384510791485</v>
       </c>
       <c r="E42">
-        <v>342.5600000000002</v>
+        <v>397.5940000000003</v>
       </c>
       <c r="F42">
-        <v>2201.36</v>
+        <v>2256.394</v>
       </c>
       <c r="G42">
         <v>275.2</v>
@@ -4737,28 +4737,28 @@
         <v>681.7</v>
       </c>
       <c r="M42">
-        <v>121.735208</v>
+        <v>124.7785882</v>
       </c>
       <c r="N42">
-        <v>559.964792</v>
+        <v>556.9214118</v>
       </c>
       <c r="O42">
-        <v>139.991198</v>
+        <v>139.23035295</v>
       </c>
       <c r="P42">
-        <v>419.973594</v>
+        <v>417.69105885</v>
       </c>
       <c r="Q42">
-        <v>745.8735939999999</v>
+        <v>743.59105885</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1334349572363388</v>
+        <v>0.134672739118208</v>
       </c>
       <c r="T42">
-        <v>1.206328172592776</v>
+        <v>1.223366706103974</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.599858998885515</v>
+        <v>5.463277072083429</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09646166607974274</v>
+        <v>0.09627235781768219</v>
       </c>
       <c r="C43">
-        <v>3957.190510791484</v>
+        <v>3924.429796601632</v>
       </c>
       <c r="D43">
-        <v>5938.384510791485</v>
+        <v>5960.657796601632</v>
       </c>
       <c r="E43">
-        <v>397.5940000000003</v>
+        <v>452.6279999999999</v>
       </c>
       <c r="F43">
-        <v>2256.394</v>
+        <v>2311.428</v>
       </c>
       <c r="G43">
         <v>275.2</v>
@@ -4819,28 +4819,28 @@
         <v>681.7</v>
       </c>
       <c r="M43">
-        <v>124.7785882</v>
+        <v>127.8219684</v>
       </c>
       <c r="N43">
-        <v>556.9214118</v>
+        <v>553.8780316</v>
       </c>
       <c r="O43">
-        <v>139.23035295</v>
+        <v>138.4695079</v>
       </c>
       <c r="P43">
-        <v>417.69105885</v>
+        <v>415.4085237</v>
       </c>
       <c r="Q43">
-        <v>743.59105885</v>
+        <v>741.3085237</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.134672739118208</v>
+        <v>0.1359532031339348</v>
       </c>
       <c r="T43">
-        <v>1.223366706103974</v>
+        <v>1.240992775253488</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.463277072083429</v>
+        <v>5.333199046557634</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0962723578176822</v>
+        <v>0.09608304955562161</v>
       </c>
       <c r="C44">
-        <v>3924.42979660163</v>
+        <v>3891.836793680862</v>
       </c>
       <c r="D44">
-        <v>5960.65779660163</v>
+        <v>5983.098793680862</v>
       </c>
       <c r="E44">
-        <v>452.6279999999999</v>
+        <v>507.662</v>
       </c>
       <c r="F44">
-        <v>2311.428</v>
+        <v>2366.462</v>
       </c>
       <c r="G44">
         <v>275.2</v>
@@ -4901,28 +4901,28 @@
         <v>681.7</v>
       </c>
       <c r="M44">
-        <v>127.8219684</v>
+        <v>130.8653486</v>
       </c>
       <c r="N44">
-        <v>553.8780316</v>
+        <v>550.8346514</v>
       </c>
       <c r="O44">
-        <v>138.4695079</v>
+        <v>137.70866285</v>
       </c>
       <c r="P44">
-        <v>415.4085237</v>
+        <v>413.12598855</v>
       </c>
       <c r="Q44">
-        <v>741.3085237</v>
+        <v>739.02598855</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1359532031339348</v>
+        <v>0.1372785957116169</v>
       </c>
       <c r="T44">
-        <v>1.240992775253488</v>
+        <v>1.259237302969652</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.333199046557634</v>
+        <v>5.209171161753968</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09608304955562161</v>
+        <v>0.09589374129356107</v>
       </c>
       <c r="C45">
-        <v>3891.836793680862</v>
+        <v>3859.413403412138</v>
       </c>
       <c r="D45">
-        <v>5983.098793680862</v>
+        <v>6005.709403412138</v>
       </c>
       <c r="E45">
-        <v>507.662</v>
+        <v>562.6959999999997</v>
       </c>
       <c r="F45">
-        <v>2366.462</v>
+        <v>2421.496</v>
       </c>
       <c r="G45">
         <v>275.2</v>
@@ -4983,28 +4983,28 @@
         <v>681.7</v>
       </c>
       <c r="M45">
-        <v>130.8653486</v>
+        <v>133.9087288</v>
       </c>
       <c r="N45">
-        <v>550.8346514</v>
+        <v>547.7912712000001</v>
       </c>
       <c r="O45">
-        <v>137.70866285</v>
+        <v>136.9478178</v>
       </c>
       <c r="P45">
-        <v>413.12598855</v>
+        <v>410.8434534</v>
       </c>
       <c r="Q45">
-        <v>739.02598855</v>
+        <v>736.7434534</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1372785957116169</v>
+        <v>0.1386513237385019</v>
       </c>
       <c r="T45">
-        <v>1.259237302969652</v>
+        <v>1.278133420961394</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.209171161753968</v>
+        <v>5.090780908077742</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09589374129356107</v>
+        <v>0.09570443303150047</v>
       </c>
       <c r="C46">
-        <v>3859.413403412138</v>
+        <v>3827.161556029388</v>
       </c>
       <c r="D46">
-        <v>6005.709403412138</v>
+        <v>6028.491556029388</v>
       </c>
       <c r="E46">
-        <v>562.6959999999997</v>
+        <v>617.7299999999998</v>
       </c>
       <c r="F46">
-        <v>2421.496</v>
+        <v>2476.53</v>
       </c>
       <c r="G46">
         <v>275.2</v>
@@ -5065,28 +5065,28 @@
         <v>681.7</v>
       </c>
       <c r="M46">
-        <v>133.9087288</v>
+        <v>136.952109</v>
       </c>
       <c r="N46">
-        <v>547.7912712000001</v>
+        <v>544.7478910000001</v>
       </c>
       <c r="O46">
-        <v>136.9478178</v>
+        <v>136.18697275</v>
       </c>
       <c r="P46">
-        <v>410.8434534</v>
+        <v>408.5609182500001</v>
       </c>
       <c r="Q46">
-        <v>736.7434534</v>
+        <v>734.4609182500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1386513237385019</v>
+        <v>0.1400739691481827</v>
       </c>
       <c r="T46">
-        <v>1.278133420961394</v>
+        <v>1.297716670516471</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.090780908077742</v>
+        <v>4.977652443453793</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09570443303150047</v>
+        <v>0.09551512476943992</v>
       </c>
       <c r="C47">
-        <v>3827.161556029388</v>
+        <v>3795.083211166759</v>
       </c>
       <c r="D47">
-        <v>6028.491556029388</v>
+        <v>6051.447211166759</v>
       </c>
       <c r="E47">
-        <v>617.7299999999998</v>
+        <v>672.7639999999999</v>
       </c>
       <c r="F47">
-        <v>2476.53</v>
+        <v>2531.564</v>
       </c>
       <c r="G47">
         <v>275.2</v>
@@ -5147,28 +5147,28 @@
         <v>681.7</v>
       </c>
       <c r="M47">
-        <v>136.952109</v>
+        <v>139.9954892</v>
       </c>
       <c r="N47">
-        <v>544.7478910000001</v>
+        <v>541.7045108</v>
       </c>
       <c r="O47">
-        <v>136.18697275</v>
+        <v>135.4261277</v>
       </c>
       <c r="P47">
-        <v>408.5609182500001</v>
+        <v>406.2783831</v>
       </c>
       <c r="Q47">
-        <v>734.4609182500001</v>
+        <v>732.1783831</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1400739691481827</v>
+        <v>0.1415493051285924</v>
       </c>
       <c r="T47">
-        <v>1.297716670516471</v>
+        <v>1.318025225610626</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.977652443453793</v>
+        <v>4.869442607726535</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09551512476943992</v>
+        <v>0.09532581650737935</v>
       </c>
       <c r="C48">
-        <v>3795.083211166759</v>
+        <v>3763.180358420565</v>
       </c>
       <c r="D48">
-        <v>6051.447211166759</v>
+        <v>6074.578358420566</v>
       </c>
       <c r="E48">
-        <v>672.7639999999999</v>
+        <v>727.798</v>
       </c>
       <c r="F48">
-        <v>2531.564</v>
+        <v>2586.598</v>
       </c>
       <c r="G48">
         <v>275.2</v>
@@ -5229,28 +5229,28 @@
         <v>681.7</v>
       </c>
       <c r="M48">
-        <v>139.9954892</v>
+        <v>143.0388694</v>
       </c>
       <c r="N48">
-        <v>541.7045108</v>
+        <v>538.6611306</v>
       </c>
       <c r="O48">
-        <v>135.4261277</v>
+        <v>134.66528265</v>
       </c>
       <c r="P48">
-        <v>406.2783831</v>
+        <v>403.99584795</v>
       </c>
       <c r="Q48">
-        <v>732.1783831</v>
+        <v>729.89584795</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1415493051285924</v>
+        <v>0.1430803141648667</v>
       </c>
       <c r="T48">
-        <v>1.318025225610626</v>
+        <v>1.339100141274371</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.869442607726535</v>
+        <v>4.765837445860013</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09532581650737935</v>
+        <v>0.09513650824531877</v>
       </c>
       <c r="C49">
-        <v>3763.180358420565</v>
+        <v>3731.455017924099</v>
       </c>
       <c r="D49">
-        <v>6074.578358420566</v>
+        <v>6097.887017924099</v>
       </c>
       <c r="E49">
-        <v>727.798</v>
+        <v>782.8320000000001</v>
       </c>
       <c r="F49">
-        <v>2586.598</v>
+        <v>2641.632</v>
       </c>
       <c r="G49">
         <v>275.2</v>
@@ -5311,28 +5311,28 @@
         <v>681.7</v>
       </c>
       <c r="M49">
-        <v>143.0388694</v>
+        <v>146.0822496</v>
       </c>
       <c r="N49">
-        <v>538.6611306</v>
+        <v>535.6177504</v>
       </c>
       <c r="O49">
-        <v>134.66528265</v>
+        <v>133.9044376</v>
       </c>
       <c r="P49">
-        <v>403.99584795</v>
+        <v>401.7133128</v>
       </c>
       <c r="Q49">
-        <v>729.89584795</v>
+        <v>727.6133127999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1430803141648667</v>
+        <v>0.1446702081640746</v>
       </c>
       <c r="T49">
-        <v>1.339100141274371</v>
+        <v>1.360985630617491</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.765837445860013</v>
+        <v>4.666549165737929</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09513650824531877</v>
+        <v>0.09494719998325823</v>
       </c>
       <c r="C50">
-        <v>3731.4550179241</v>
+        <v>3699.909240935746</v>
       </c>
       <c r="D50">
-        <v>6097.887017924099</v>
+        <v>6121.375240935746</v>
       </c>
       <c r="E50">
-        <v>782.8319999999997</v>
+        <v>837.8659999999998</v>
       </c>
       <c r="F50">
-        <v>2641.632</v>
+        <v>2696.666</v>
       </c>
       <c r="G50">
         <v>275.2</v>
@@ -5393,28 +5393,28 @@
         <v>681.7</v>
       </c>
       <c r="M50">
-        <v>146.0822496</v>
+        <v>149.1256298</v>
       </c>
       <c r="N50">
-        <v>535.6177504000001</v>
+        <v>532.5743702000001</v>
       </c>
       <c r="O50">
-        <v>133.9044376</v>
+        <v>133.14359255</v>
       </c>
       <c r="P50">
-        <v>401.7133128</v>
+        <v>399.4307776500001</v>
       </c>
       <c r="Q50">
-        <v>727.6133128</v>
+        <v>725.3307776500001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1446702081640746</v>
+        <v>0.1463224509475652</v>
       </c>
       <c r="T50">
-        <v>1.360985630617491</v>
+        <v>1.383729374444655</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.666549165737931</v>
+        <v>4.571313468477973</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09494719998325823</v>
+        <v>0.09569539172119766</v>
       </c>
       <c r="C51">
-        <v>3699.909240935746</v>
+        <v>3553.083950756349</v>
       </c>
       <c r="D51">
-        <v>6121.375240935746</v>
+        <v>6029.583950756349</v>
       </c>
       <c r="E51">
-        <v>837.8659999999998</v>
+        <v>892.8999999999999</v>
       </c>
       <c r="F51">
-        <v>2696.666</v>
+        <v>2751.7</v>
       </c>
       <c r="G51">
         <v>275.2</v>
@@ -5475,45 +5475,45 @@
         <v>681.7</v>
       </c>
       <c r="M51">
-        <v>149.1256298</v>
+        <v>159.04826</v>
       </c>
       <c r="N51">
-        <v>532.5743702000001</v>
+        <v>522.65174</v>
       </c>
       <c r="O51">
-        <v>133.14359255</v>
+        <v>130.662935</v>
       </c>
       <c r="P51">
-        <v>399.4307776500001</v>
+        <v>391.988805</v>
       </c>
       <c r="Q51">
-        <v>725.3307776500001</v>
+        <v>717.888805</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1463224509475652</v>
+        <v>0.1480407834423953</v>
       </c>
       <c r="T51">
-        <v>1.383729374444655</v>
+        <v>1.407382868024906</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.571313468477973</v>
+        <v>4.286120451742132</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09569539172119766</v>
+        <v>0.09552483345913709</v>
       </c>
       <c r="C52">
-        <v>3553.083950756349</v>
+        <v>3518.731676325816</v>
       </c>
       <c r="D52">
-        <v>6029.583950756349</v>
+        <v>6050.265676325816</v>
       </c>
       <c r="E52">
-        <v>892.8999999999999</v>
+        <v>947.934</v>
       </c>
       <c r="F52">
-        <v>2751.7</v>
+        <v>2806.734</v>
       </c>
       <c r="G52">
         <v>275.2</v>
@@ -5557,28 +5557,28 @@
         <v>681.7</v>
       </c>
       <c r="M52">
-        <v>159.04826</v>
+        <v>162.2292252</v>
       </c>
       <c r="N52">
-        <v>522.65174</v>
+        <v>519.4707748000001</v>
       </c>
       <c r="O52">
-        <v>130.662935</v>
+        <v>129.8676937</v>
       </c>
       <c r="P52">
-        <v>391.988805</v>
+        <v>389.6030811000001</v>
       </c>
       <c r="Q52">
-        <v>717.888805</v>
+        <v>715.5030811</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1480407834423953</v>
+        <v>0.1498292519574226</v>
       </c>
       <c r="T52">
-        <v>1.407382868024906</v>
+        <v>1.432001810322717</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.286120451742132</v>
+        <v>4.202078874256992</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09552483345913709</v>
+        <v>0.09535427519707654</v>
       </c>
       <c r="C53">
-        <v>3518.731676325816</v>
+        <v>3484.521768589397</v>
       </c>
       <c r="D53">
-        <v>6050.265676325816</v>
+        <v>6071.089768589397</v>
       </c>
       <c r="E53">
-        <v>947.934</v>
+        <v>1002.968</v>
       </c>
       <c r="F53">
-        <v>2806.734</v>
+        <v>2861.768</v>
       </c>
       <c r="G53">
         <v>275.2</v>
@@ -5639,28 +5639,28 @@
         <v>681.7</v>
       </c>
       <c r="M53">
-        <v>162.2292252</v>
+        <v>165.4101904</v>
       </c>
       <c r="N53">
-        <v>519.4707748000001</v>
+        <v>516.2898096</v>
       </c>
       <c r="O53">
-        <v>129.8676937</v>
+        <v>129.0724524</v>
       </c>
       <c r="P53">
-        <v>389.6030811000001</v>
+        <v>387.2173572</v>
       </c>
       <c r="Q53">
-        <v>715.5030811</v>
+        <v>713.1173572</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1498292519574226</v>
+        <v>0.1516922399939094</v>
       </c>
       <c r="T53">
-        <v>1.432001810322717</v>
+        <v>1.457646541882938</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.202078874256992</v>
+        <v>4.121269665136666</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09535427519707654</v>
+        <v>0.09518371693501597</v>
       </c>
       <c r="C54">
-        <v>3484.521768589397</v>
+        <v>3450.455702637513</v>
       </c>
       <c r="D54">
-        <v>6071.089768589397</v>
+        <v>6092.057702637513</v>
       </c>
       <c r="E54">
-        <v>1002.968</v>
+        <v>1058.002</v>
       </c>
       <c r="F54">
-        <v>2861.768</v>
+        <v>2916.802</v>
       </c>
       <c r="G54">
         <v>275.2</v>
@@ -5721,28 +5721,28 @@
         <v>681.7</v>
       </c>
       <c r="M54">
-        <v>165.4101904</v>
+        <v>168.5911556</v>
       </c>
       <c r="N54">
-        <v>516.2898096</v>
+        <v>513.1088444000001</v>
       </c>
       <c r="O54">
-        <v>129.0724524</v>
+        <v>128.2772111</v>
       </c>
       <c r="P54">
-        <v>387.2173572</v>
+        <v>384.8316333</v>
       </c>
       <c r="Q54">
-        <v>713.1173572</v>
+        <v>710.7316333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1516922399939094</v>
+        <v>0.1536345041170553</v>
       </c>
       <c r="T54">
-        <v>1.457646541882938</v>
+        <v>1.484382538615934</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.121269665136666</v>
+        <v>4.043509860134087</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09518371693501597</v>
+        <v>0.0964306586729554</v>
       </c>
       <c r="C55">
-        <v>3450.455702637513</v>
+        <v>3245.385317205068</v>
       </c>
       <c r="D55">
-        <v>6092.057702637513</v>
+        <v>5942.021317205068</v>
       </c>
       <c r="E55">
-        <v>1058.002</v>
+        <v>1113.036</v>
       </c>
       <c r="F55">
-        <v>2916.802</v>
+        <v>2971.836</v>
       </c>
       <c r="G55">
         <v>275.2</v>
@@ -5803,45 +5803,45 @@
         <v>681.7</v>
       </c>
       <c r="M55">
-        <v>168.5911556</v>
+        <v>182.1735468</v>
       </c>
       <c r="N55">
-        <v>513.1088444000001</v>
+        <v>499.5264532</v>
       </c>
       <c r="O55">
-        <v>128.2772111</v>
+        <v>124.8816133</v>
       </c>
       <c r="P55">
-        <v>384.8316333</v>
+        <v>374.6448399</v>
       </c>
       <c r="Q55">
-        <v>710.7316333</v>
+        <v>700.5448398999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1536345041170553</v>
+        <v>0.1556612145064248</v>
       </c>
       <c r="T55">
-        <v>1.484382538615934</v>
+        <v>1.512280969989495</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.043509860134087</v>
+        <v>3.742036162629074</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0964306586729554</v>
+        <v>0.09628635041089484</v>
       </c>
       <c r="C56">
-        <v>3245.385317205068</v>
+        <v>3207.335764732645</v>
       </c>
       <c r="D56">
-        <v>5942.021317205068</v>
+        <v>5959.005764732645</v>
       </c>
       <c r="E56">
-        <v>1113.036</v>
+        <v>1168.07</v>
       </c>
       <c r="F56">
-        <v>2971.836</v>
+        <v>3026.87</v>
       </c>
       <c r="G56">
         <v>275.2</v>
@@ -5885,28 +5885,28 @@
         <v>681.7</v>
       </c>
       <c r="M56">
-        <v>182.1735468</v>
+        <v>185.547131</v>
       </c>
       <c r="N56">
-        <v>499.5264532</v>
+        <v>496.152869</v>
       </c>
       <c r="O56">
-        <v>124.8816133</v>
+        <v>124.03821725</v>
       </c>
       <c r="P56">
-        <v>374.6448399</v>
+        <v>372.11465175</v>
       </c>
       <c r="Q56">
-        <v>700.5448398999999</v>
+        <v>698.01465175</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1556612145064248</v>
+        <v>0.1577780009130997</v>
       </c>
       <c r="T56">
-        <v>1.512280969989495</v>
+        <v>1.541419331646325</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.742036162629074</v>
+        <v>3.673999141490363</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09628635041089484</v>
+        <v>0.09614204214883428</v>
       </c>
       <c r="C57">
-        <v>3207.335764732645</v>
+        <v>3169.383585986043</v>
       </c>
       <c r="D57">
-        <v>5959.005764732645</v>
+        <v>5976.087585986043</v>
       </c>
       <c r="E57">
-        <v>1168.07</v>
+        <v>1223.104</v>
       </c>
       <c r="F57">
-        <v>3026.87</v>
+        <v>3081.904</v>
       </c>
       <c r="G57">
         <v>275.2</v>
@@ -5967,28 +5967,28 @@
         <v>681.7</v>
       </c>
       <c r="M57">
-        <v>185.547131</v>
+        <v>188.9207152</v>
       </c>
       <c r="N57">
-        <v>496.152869</v>
+        <v>492.7792848</v>
       </c>
       <c r="O57">
-        <v>124.03821725</v>
+        <v>123.1948212</v>
       </c>
       <c r="P57">
-        <v>372.11465175</v>
+        <v>369.5844636</v>
       </c>
       <c r="Q57">
-        <v>698.01465175</v>
+        <v>695.4844636</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1577780009130997</v>
+        <v>0.1599910048837143</v>
       </c>
       <c r="T57">
-        <v>1.541419331646325</v>
+        <v>1.571882164287557</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.673999141490363</v>
+        <v>3.60839201396375</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09614204214883428</v>
+        <v>0.09599773388677371</v>
       </c>
       <c r="C58">
-        <v>3169.383585986043</v>
+        <v>3131.529620754157</v>
       </c>
       <c r="D58">
-        <v>5976.087585986043</v>
+        <v>5993.267620754157</v>
       </c>
       <c r="E58">
-        <v>1223.104</v>
+        <v>1278.138</v>
       </c>
       <c r="F58">
-        <v>3081.904</v>
+        <v>3136.938</v>
       </c>
       <c r="G58">
         <v>275.2</v>
@@ -6049,28 +6049,28 @@
         <v>681.7</v>
       </c>
       <c r="M58">
-        <v>188.9207152</v>
+        <v>192.2942994</v>
       </c>
       <c r="N58">
-        <v>492.7792848</v>
+        <v>489.4057006</v>
       </c>
       <c r="O58">
-        <v>123.1948212</v>
+        <v>122.35142515</v>
       </c>
       <c r="P58">
-        <v>369.5844636</v>
+        <v>367.05427545</v>
       </c>
       <c r="Q58">
-        <v>695.4844636</v>
+        <v>692.9542754500001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1599910048837143</v>
+        <v>0.1623069392715668</v>
       </c>
       <c r="T58">
-        <v>1.571882164287557</v>
+        <v>1.60376187286559</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.60839201396375</v>
+        <v>3.545086890911755</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09599773388677371</v>
+        <v>0.09707142562471315</v>
       </c>
       <c r="C59">
-        <v>3131.529620754157</v>
+        <v>2950.988638077982</v>
       </c>
       <c r="D59">
-        <v>5993.267620754157</v>
+        <v>5867.760638077983</v>
       </c>
       <c r="E59">
-        <v>1278.138</v>
+        <v>1333.172</v>
       </c>
       <c r="F59">
-        <v>3136.938</v>
+        <v>3191.972</v>
       </c>
       <c r="G59">
         <v>275.2</v>
@@ -6131,45 +6131,45 @@
         <v>681.7</v>
       </c>
       <c r="M59">
-        <v>192.2942994</v>
+        <v>204.6054052</v>
       </c>
       <c r="N59">
-        <v>489.4057006</v>
+        <v>477.0945948</v>
       </c>
       <c r="O59">
-        <v>122.35142515</v>
+        <v>119.2736487</v>
       </c>
       <c r="P59">
-        <v>367.05427545</v>
+        <v>357.8209461</v>
       </c>
       <c r="Q59">
-        <v>692.9542754500001</v>
+        <v>683.7209461</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1623069392715668</v>
+        <v>0.164733156249317</v>
       </c>
       <c r="T59">
-        <v>1.60376187286559</v>
+        <v>1.637159662804482</v>
       </c>
       <c r="U59">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.545086890911755</v>
+        <v>3.331779037477745</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09707142562471315</v>
+        <v>0.09694811736265259</v>
       </c>
       <c r="C60">
-        <v>2950.988638077983</v>
+        <v>2910.10067910113</v>
       </c>
       <c r="D60">
-        <v>5867.760638077983</v>
+        <v>5881.906679101129</v>
       </c>
       <c r="E60">
-        <v>1333.172</v>
+        <v>1388.205999999999</v>
       </c>
       <c r="F60">
-        <v>3191.972</v>
+        <v>3247.005999999999</v>
       </c>
       <c r="G60">
         <v>275.2</v>
@@ -6213,28 +6213,28 @@
         <v>681.7</v>
       </c>
       <c r="M60">
-        <v>204.6054052</v>
+        <v>208.1330846</v>
       </c>
       <c r="N60">
-        <v>477.0945948</v>
+        <v>473.5669154000001</v>
       </c>
       <c r="O60">
-        <v>119.2736487</v>
+        <v>118.39172885</v>
       </c>
       <c r="P60">
-        <v>357.8209461</v>
+        <v>355.17518655</v>
       </c>
       <c r="Q60">
-        <v>683.7209461</v>
+        <v>681.07518655</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.164733156249317</v>
+        <v>0.1672777252747624</v>
       </c>
       <c r="T60">
-        <v>1.637159662804482</v>
+        <v>1.672186613228198</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.331779037477745</v>
+        <v>3.275308206334055</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09694811736265259</v>
+        <v>0.09682480910059202</v>
       </c>
       <c r="C61">
-        <v>2910.10067910113</v>
+        <v>2869.28109171701</v>
       </c>
       <c r="D61">
-        <v>5881.906679101129</v>
+        <v>5896.12109171701</v>
       </c>
       <c r="E61">
-        <v>1388.205999999999</v>
+        <v>1443.24</v>
       </c>
       <c r="F61">
-        <v>3247.005999999999</v>
+        <v>3302.04</v>
       </c>
       <c r="G61">
         <v>275.2</v>
@@ -6295,28 +6295,28 @@
         <v>681.7</v>
       </c>
       <c r="M61">
-        <v>208.1330846</v>
+        <v>211.660764</v>
       </c>
       <c r="N61">
-        <v>473.5669154000001</v>
+        <v>470.0392360000001</v>
       </c>
       <c r="O61">
-        <v>118.39172885</v>
+        <v>117.509809</v>
       </c>
       <c r="P61">
-        <v>355.17518655</v>
+        <v>352.5294270000001</v>
       </c>
       <c r="Q61">
-        <v>681.07518655</v>
+        <v>678.429427</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1672777252747624</v>
+        <v>0.16994952275148</v>
       </c>
       <c r="T61">
-        <v>1.672186613228198</v>
+        <v>1.7089649111731</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.275308206334055</v>
+        <v>3.220719736228487</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09682480910059202</v>
+        <v>0.09670150083853146</v>
       </c>
       <c r="C62">
-        <v>2869.28109171701</v>
+        <v>2828.530372813663</v>
       </c>
       <c r="D62">
-        <v>5896.12109171701</v>
+        <v>5910.404372813663</v>
       </c>
       <c r="E62">
-        <v>1443.24</v>
+        <v>1498.274</v>
       </c>
       <c r="F62">
-        <v>3302.04</v>
+        <v>3357.074</v>
       </c>
       <c r="G62">
         <v>275.2</v>
@@ -6377,28 +6377,28 @@
         <v>681.7</v>
       </c>
       <c r="M62">
-        <v>211.660764</v>
+        <v>215.1884434</v>
       </c>
       <c r="N62">
-        <v>470.0392360000001</v>
+        <v>466.5115566000001</v>
       </c>
       <c r="O62">
-        <v>117.509809</v>
+        <v>116.62788915</v>
       </c>
       <c r="P62">
-        <v>352.5294270000001</v>
+        <v>349.8836674500001</v>
       </c>
       <c r="Q62">
-        <v>678.429427</v>
+        <v>675.7836674500001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.16994952275148</v>
+        <v>0.172758335483414</v>
       </c>
       <c r="T62">
-        <v>1.7089649111731</v>
+        <v>1.747629275679279</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.220719736228487</v>
+        <v>3.16792105202802</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09670150083853146</v>
+        <v>0.09657819257647089</v>
       </c>
       <c r="C63">
-        <v>2828.530372813663</v>
+        <v>2787.849024105637</v>
       </c>
       <c r="D63">
-        <v>5910.404372813663</v>
+        <v>5924.757024105637</v>
       </c>
       <c r="E63">
-        <v>1498.274</v>
+        <v>1553.308</v>
       </c>
       <c r="F63">
-        <v>3357.074</v>
+        <v>3412.108</v>
       </c>
       <c r="G63">
         <v>275.2</v>
@@ -6459,28 +6459,28 @@
         <v>681.7</v>
       </c>
       <c r="M63">
-        <v>215.1884434</v>
+        <v>218.7161228</v>
       </c>
       <c r="N63">
-        <v>466.5115566000001</v>
+        <v>462.9838772000001</v>
       </c>
       <c r="O63">
-        <v>116.62788915</v>
+        <v>115.7459693</v>
       </c>
       <c r="P63">
-        <v>349.8836674500001</v>
+        <v>347.2379079</v>
       </c>
       <c r="Q63">
-        <v>675.7836674500001</v>
+        <v>673.1379079000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.172758335483414</v>
+        <v>0.1757149804643971</v>
       </c>
       <c r="T63">
-        <v>1.747629275679279</v>
+        <v>1.788328606738414</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.16792105202802</v>
+        <v>3.116825551188859</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09657819257647089</v>
+        <v>0.09645488431441032</v>
       </c>
       <c r="C64">
-        <v>2787.849024105637</v>
+        <v>2747.237552192743</v>
       </c>
       <c r="D64">
-        <v>5924.757024105637</v>
+        <v>5939.179552192743</v>
       </c>
       <c r="E64">
-        <v>1553.308</v>
+        <v>1608.342</v>
       </c>
       <c r="F64">
-        <v>3412.108</v>
+        <v>3467.142</v>
       </c>
       <c r="G64">
         <v>275.2</v>
@@ -6541,28 +6541,28 @@
         <v>681.7</v>
       </c>
       <c r="M64">
-        <v>218.7161228</v>
+        <v>222.2438022</v>
       </c>
       <c r="N64">
-        <v>462.9838772000001</v>
+        <v>459.4561978</v>
       </c>
       <c r="O64">
-        <v>115.7459693</v>
+        <v>114.86404945</v>
       </c>
       <c r="P64">
-        <v>347.2379079</v>
+        <v>344.59214835</v>
       </c>
       <c r="Q64">
-        <v>673.1379079000001</v>
+        <v>670.49214835</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1757149804643971</v>
+        <v>0.1788314440930009</v>
       </c>
       <c r="T64">
-        <v>1.788328606738414</v>
+        <v>1.831227901638584</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.116825551188859</v>
+        <v>3.067352129741416</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09645488431441032</v>
+        <v>0.09633157605234977</v>
       </c>
       <c r="C65">
-        <v>2747.237552192743</v>
+        <v>2706.696468619647</v>
       </c>
       <c r="D65">
-        <v>5939.179552192743</v>
+        <v>5953.672468619647</v>
       </c>
       <c r="E65">
-        <v>1608.342</v>
+        <v>1663.376</v>
       </c>
       <c r="F65">
-        <v>3467.142</v>
+        <v>3522.176</v>
       </c>
       <c r="G65">
         <v>275.2</v>
@@ -6623,28 +6623,28 @@
         <v>681.7</v>
       </c>
       <c r="M65">
-        <v>222.2438022</v>
+        <v>225.7714816</v>
       </c>
       <c r="N65">
-        <v>459.4561978</v>
+        <v>455.9285184</v>
       </c>
       <c r="O65">
-        <v>114.86404945</v>
+        <v>113.9821296</v>
       </c>
       <c r="P65">
-        <v>344.59214835</v>
+        <v>341.9463888</v>
       </c>
       <c r="Q65">
-        <v>670.49214835</v>
+        <v>667.8463888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1788314440930009</v>
+        <v>0.1821210445898604</v>
       </c>
       <c r="T65">
-        <v>1.831227901638584</v>
+        <v>1.876510490699874</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.067352129741416</v>
+        <v>3.019424752714206</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09633157605234977</v>
+        <v>0.1000107677902892</v>
       </c>
       <c r="C66">
-        <v>2706.696468619647</v>
+        <v>2247.596939762358</v>
       </c>
       <c r="D66">
-        <v>5953.672468619647</v>
+        <v>5549.606939762358</v>
       </c>
       <c r="E66">
-        <v>1663.376</v>
+        <v>1718.41</v>
       </c>
       <c r="F66">
-        <v>3522.176</v>
+        <v>3577.21</v>
       </c>
       <c r="G66">
         <v>275.2</v>
@@ -6705,45 +6705,45 @@
         <v>681.7</v>
       </c>
       <c r="M66">
-        <v>225.7714816</v>
+        <v>257.201399</v>
       </c>
       <c r="N66">
-        <v>455.9285184</v>
+        <v>424.498601</v>
       </c>
       <c r="O66">
-        <v>113.9821296</v>
+        <v>106.12465025</v>
       </c>
       <c r="P66">
-        <v>341.9463888</v>
+        <v>318.37395075</v>
       </c>
       <c r="Q66">
-        <v>667.8463888</v>
+        <v>644.27395075</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1821210445898604</v>
+        <v>0.1855986222579691</v>
       </c>
       <c r="T66">
-        <v>1.876510490699874</v>
+        <v>1.924380656278953</v>
       </c>
       <c r="U66">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.019424752714206</v>
+        <v>2.650452146257571</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1000107677902892</v>
+        <v>0.09994595952822863</v>
       </c>
       <c r="C67">
-        <v>2247.596939762358</v>
+        <v>2199.205363020141</v>
       </c>
       <c r="D67">
-        <v>5549.606939762358</v>
+        <v>5556.249363020142</v>
       </c>
       <c r="E67">
-        <v>1718.41</v>
+        <v>1773.444</v>
       </c>
       <c r="F67">
-        <v>3577.21</v>
+        <v>3632.244</v>
       </c>
       <c r="G67">
         <v>275.2</v>
@@ -6787,28 +6787,28 @@
         <v>681.7</v>
       </c>
       <c r="M67">
-        <v>257.201399</v>
+        <v>261.1583436</v>
       </c>
       <c r="N67">
-        <v>424.498601</v>
+        <v>420.5416564</v>
       </c>
       <c r="O67">
-        <v>106.12465025</v>
+        <v>105.1354141</v>
       </c>
       <c r="P67">
-        <v>318.37395075</v>
+        <v>315.4062423</v>
       </c>
       <c r="Q67">
-        <v>644.27395075</v>
+        <v>641.3062423</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1855986222579691</v>
+        <v>0.1892807633183195</v>
       </c>
       <c r="T67">
-        <v>1.924380656278953</v>
+        <v>1.975066713950918</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.650452146257571</v>
+        <v>2.610293780405184</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09994595952822863</v>
+        <v>0.09988115126616806</v>
       </c>
       <c r="C68">
-        <v>2199.205363020141</v>
+        <v>2150.829706201857</v>
       </c>
       <c r="D68">
-        <v>5556.249363020142</v>
+        <v>5562.907706201857</v>
       </c>
       <c r="E68">
-        <v>1773.444</v>
+        <v>1828.478</v>
       </c>
       <c r="F68">
-        <v>3632.244</v>
+        <v>3687.278</v>
       </c>
       <c r="G68">
         <v>275.2</v>
@@ -6869,28 +6869,28 @@
         <v>681.7</v>
       </c>
       <c r="M68">
-        <v>261.1583436</v>
+        <v>265.1152882</v>
       </c>
       <c r="N68">
-        <v>420.5416564</v>
+        <v>416.5847118</v>
       </c>
       <c r="O68">
-        <v>105.1354141</v>
+        <v>104.14617795</v>
       </c>
       <c r="P68">
-        <v>315.4062423</v>
+        <v>312.43853385</v>
       </c>
       <c r="Q68">
-        <v>641.3062423</v>
+        <v>638.33853385</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1892807633183195</v>
+        <v>0.1931860644429335</v>
       </c>
       <c r="T68">
-        <v>1.975066713950918</v>
+        <v>2.028824653906033</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.610293780405184</v>
+        <v>2.57133417174242</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09988115126616806</v>
+        <v>0.09981634300410749</v>
       </c>
       <c r="C69">
-        <v>2150.829706201857</v>
+        <v>2102.470026609199</v>
       </c>
       <c r="D69">
-        <v>5562.907706201857</v>
+        <v>5569.582026609199</v>
       </c>
       <c r="E69">
-        <v>1828.478</v>
+        <v>1883.512</v>
       </c>
       <c r="F69">
-        <v>3687.278</v>
+        <v>3742.312</v>
       </c>
       <c r="G69">
         <v>275.2</v>
@@ -6951,28 +6951,28 @@
         <v>681.7</v>
       </c>
       <c r="M69">
-        <v>265.1152882</v>
+        <v>269.0722328</v>
       </c>
       <c r="N69">
-        <v>416.5847118</v>
+        <v>412.6277672000001</v>
       </c>
       <c r="O69">
-        <v>104.14617795</v>
+        <v>103.1569418</v>
       </c>
       <c r="P69">
-        <v>312.43853385</v>
+        <v>309.4708254</v>
       </c>
       <c r="Q69">
-        <v>638.33853385</v>
+        <v>635.3708254000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1931860644429335</v>
+        <v>0.197335446887836</v>
       </c>
       <c r="T69">
-        <v>2.028824653906033</v>
+        <v>2.085942465108343</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.57133417174242</v>
+        <v>2.533520433922679</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09981634300410749</v>
+        <v>0.1017697847420469</v>
       </c>
       <c r="C70">
-        <v>2102.470026609199</v>
+        <v>1853.048035949619</v>
       </c>
       <c r="D70">
-        <v>5569.582026609199</v>
+        <v>5375.194035949619</v>
       </c>
       <c r="E70">
-        <v>1883.512</v>
+        <v>1938.546</v>
       </c>
       <c r="F70">
-        <v>3742.312</v>
+        <v>3797.346</v>
       </c>
       <c r="G70">
         <v>275.2</v>
@@ -7033,45 +7033,45 @@
         <v>681.7</v>
       </c>
       <c r="M70">
-        <v>269.0722328</v>
+        <v>287.8388268</v>
       </c>
       <c r="N70">
-        <v>412.6277672000001</v>
+        <v>393.8611732</v>
       </c>
       <c r="O70">
-        <v>103.1569418</v>
+        <v>98.4652933</v>
       </c>
       <c r="P70">
-        <v>309.4708254</v>
+        <v>295.3958799</v>
       </c>
       <c r="Q70">
-        <v>635.3708254000001</v>
+        <v>621.2958799</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.197335446887836</v>
+        <v>0.2017525314259579</v>
       </c>
       <c r="T70">
-        <v>2.085942465108343</v>
+        <v>2.14674529638822</v>
       </c>
       <c r="U70">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.533520433922679</v>
+        <v>2.368339280626889</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1017697847420469</v>
+        <v>0.1017342264799864</v>
       </c>
       <c r="C71">
-        <v>1853.048035949619</v>
+        <v>1801.431130815945</v>
       </c>
       <c r="D71">
-        <v>5375.194035949619</v>
+        <v>5378.611130815945</v>
       </c>
       <c r="E71">
-        <v>1938.546</v>
+        <v>1993.58</v>
       </c>
       <c r="F71">
-        <v>3797.346</v>
+        <v>3852.38</v>
       </c>
       <c r="G71">
         <v>275.2</v>
@@ -7115,28 +7115,28 @@
         <v>681.7</v>
       </c>
       <c r="M71">
-        <v>287.8388268</v>
+        <v>292.0104040000001</v>
       </c>
       <c r="N71">
-        <v>393.8611732</v>
+        <v>389.689596</v>
       </c>
       <c r="O71">
-        <v>98.4652933</v>
+        <v>97.422399</v>
       </c>
       <c r="P71">
-        <v>295.3958799</v>
+        <v>292.267197</v>
       </c>
       <c r="Q71">
-        <v>621.2958799</v>
+        <v>618.167197</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2017525314259579</v>
+        <v>0.2064640882666212</v>
       </c>
       <c r="T71">
-        <v>2.14674529638822</v>
+        <v>2.211601649753423</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.368339280626889</v>
+        <v>2.33450586233222</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1017342264799864</v>
+        <v>0.1016986682179258</v>
       </c>
       <c r="C72">
-        <v>1801.431130815945</v>
+        <v>1749.818573047195</v>
       </c>
       <c r="D72">
-        <v>5378.611130815945</v>
+        <v>5382.032573047195</v>
       </c>
       <c r="E72">
-        <v>1993.58</v>
+        <v>2048.614</v>
       </c>
       <c r="F72">
-        <v>3852.38</v>
+        <v>3907.414</v>
       </c>
       <c r="G72">
         <v>275.2</v>
@@ -7197,28 +7197,28 @@
         <v>681.7</v>
       </c>
       <c r="M72">
-        <v>292.0104040000001</v>
+        <v>296.1819812000001</v>
       </c>
       <c r="N72">
-        <v>389.689596</v>
+        <v>385.5180188</v>
       </c>
       <c r="O72">
-        <v>97.422399</v>
+        <v>96.3795047</v>
       </c>
       <c r="P72">
-        <v>292.267197</v>
+        <v>289.1385141</v>
       </c>
       <c r="Q72">
-        <v>618.167197</v>
+        <v>615.0385140999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2064640882666212</v>
+        <v>0.2115005800618132</v>
       </c>
       <c r="T72">
-        <v>2.211601649753423</v>
+        <v>2.280930855074847</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.33450586233222</v>
+        <v>2.30162549807402</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1016986682179258</v>
+        <v>0.1016631099558652</v>
       </c>
       <c r="C73">
-        <v>1749.818573047195</v>
+        <v>1698.210370944986</v>
       </c>
       <c r="D73">
-        <v>5382.032573047195</v>
+        <v>5385.458370944985</v>
       </c>
       <c r="E73">
-        <v>2048.614</v>
+        <v>2103.647999999999</v>
       </c>
       <c r="F73">
-        <v>3907.414</v>
+        <v>3962.447999999999</v>
       </c>
       <c r="G73">
         <v>275.2</v>
@@ -7279,28 +7279,28 @@
         <v>681.7</v>
       </c>
       <c r="M73">
-        <v>296.1819812</v>
+        <v>300.3535584</v>
       </c>
       <c r="N73">
-        <v>385.5180188</v>
+        <v>381.3464416</v>
       </c>
       <c r="O73">
-        <v>96.37950470000001</v>
+        <v>95.33661040000001</v>
       </c>
       <c r="P73">
-        <v>289.1385141000001</v>
+        <v>286.0098312</v>
       </c>
       <c r="Q73">
-        <v>615.0385141</v>
+        <v>611.9098312</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2115005800618131</v>
+        <v>0.2168968212709473</v>
       </c>
       <c r="T73">
-        <v>2.280930855074847</v>
+        <v>2.355212146490658</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.30162549807402</v>
+        <v>2.269658477267436</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1016631099558652</v>
+        <v>0.1016275516938047</v>
       </c>
       <c r="C74">
-        <v>1698.210370944986</v>
+        <v>1646.606532832089</v>
       </c>
       <c r="D74">
-        <v>5385.458370944985</v>
+        <v>5388.888532832088</v>
       </c>
       <c r="E74">
-        <v>2103.647999999999</v>
+        <v>2158.682</v>
       </c>
       <c r="F74">
-        <v>3962.447999999999</v>
+        <v>4017.482</v>
       </c>
       <c r="G74">
         <v>275.2</v>
@@ -7361,28 +7361,28 @@
         <v>681.7</v>
       </c>
       <c r="M74">
-        <v>300.3535584</v>
+        <v>304.5251356</v>
       </c>
       <c r="N74">
-        <v>381.3464416</v>
+        <v>377.1748644</v>
       </c>
       <c r="O74">
-        <v>95.33661040000001</v>
+        <v>94.29371610000001</v>
       </c>
       <c r="P74">
-        <v>286.0098312</v>
+        <v>282.8811483000001</v>
       </c>
       <c r="Q74">
-        <v>611.9098312</v>
+        <v>608.7811483</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2168968212709473</v>
+        <v>0.2226927840511284</v>
       </c>
       <c r="T74">
-        <v>2.355212146490658</v>
+        <v>2.434995755789122</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.269658477267436</v>
+        <v>2.238567265250074</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1016275516938047</v>
+        <v>0.1015919934317441</v>
       </c>
       <c r="C75">
-        <v>1646.606532832089</v>
+        <v>1595.007067052488</v>
       </c>
       <c r="D75">
-        <v>5388.888532832088</v>
+        <v>5392.323067052488</v>
       </c>
       <c r="E75">
-        <v>2158.682</v>
+        <v>2213.715999999999</v>
       </c>
       <c r="F75">
-        <v>4017.482</v>
+        <v>4072.516</v>
       </c>
       <c r="G75">
         <v>275.2</v>
@@ -7443,28 +7443,28 @@
         <v>681.7</v>
       </c>
       <c r="M75">
-        <v>304.5251356</v>
+        <v>308.6967128</v>
       </c>
       <c r="N75">
-        <v>377.1748644</v>
+        <v>373.0032872</v>
       </c>
       <c r="O75">
-        <v>94.29371610000001</v>
+        <v>93.25082180000001</v>
       </c>
       <c r="P75">
-        <v>282.8811483000001</v>
+        <v>279.7524654</v>
       </c>
       <c r="Q75">
-        <v>608.7811483</v>
+        <v>605.6524654</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2226927840511284</v>
+        <v>0.2289345901220927</v>
       </c>
       <c r="T75">
-        <v>2.434995755789122</v>
+        <v>2.520916565802852</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.238567265250074</v>
+        <v>2.208316356260208</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1015919934317441</v>
+        <v>0.1015564351696835</v>
       </c>
       <c r="C76">
-        <v>1595.007067052488</v>
+        <v>1543.411981971456</v>
       </c>
       <c r="D76">
-        <v>5392.323067052488</v>
+        <v>5395.761981971455</v>
       </c>
       <c r="E76">
-        <v>2213.715999999999</v>
+        <v>2268.749999999999</v>
       </c>
       <c r="F76">
-        <v>4072.516</v>
+        <v>4127.549999999999</v>
       </c>
       <c r="G76">
         <v>275.2</v>
@@ -7525,28 +7525,28 @@
         <v>681.7</v>
       </c>
       <c r="M76">
-        <v>308.6967128</v>
+        <v>312.8682899999999</v>
       </c>
       <c r="N76">
-        <v>373.0032872</v>
+        <v>368.8317100000001</v>
       </c>
       <c r="O76">
-        <v>93.25082180000001</v>
+        <v>92.20792750000003</v>
       </c>
       <c r="P76">
-        <v>279.7524654</v>
+        <v>276.6237825000001</v>
       </c>
       <c r="Q76">
-        <v>605.6524654</v>
+        <v>602.5237825</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2289345901220927</v>
+        <v>0.2356757406787341</v>
       </c>
       <c r="T76">
-        <v>2.520916565802852</v>
+        <v>2.613711040617682</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.208316356260208</v>
+        <v>2.17887213817674</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1015564351696835</v>
+        <v>0.101520876907623</v>
       </c>
       <c r="C77">
-        <v>1543.411981971456</v>
+        <v>1491.821285975618</v>
       </c>
       <c r="D77">
-        <v>5395.761981971455</v>
+        <v>5399.205285975618</v>
       </c>
       <c r="E77">
-        <v>2268.749999999999</v>
+        <v>2323.784</v>
       </c>
       <c r="F77">
-        <v>4127.549999999999</v>
+        <v>4182.584</v>
       </c>
       <c r="G77">
         <v>275.2</v>
@@ -7607,28 +7607,28 @@
         <v>681.7</v>
       </c>
       <c r="M77">
-        <v>312.8682899999999</v>
+        <v>317.0398672</v>
       </c>
       <c r="N77">
-        <v>368.8317100000001</v>
+        <v>364.6601328</v>
       </c>
       <c r="O77">
-        <v>92.20792750000003</v>
+        <v>91.16503320000001</v>
       </c>
       <c r="P77">
-        <v>276.6237825000001</v>
+        <v>273.4950996</v>
       </c>
       <c r="Q77">
-        <v>602.5237825</v>
+        <v>599.3950996</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2356757406787341</v>
+        <v>0.2429786537817624</v>
       </c>
       <c r="T77">
-        <v>2.613711040617682</v>
+        <v>2.714238388333746</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.17887213817674</v>
+        <v>2.150202767937571</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.101520876907623</v>
+        <v>0.1014853186455624</v>
       </c>
       <c r="C78">
-        <v>1491.821285975618</v>
+        <v>1440.234987473019</v>
       </c>
       <c r="D78">
-        <v>5399.205285975618</v>
+        <v>5402.652987473019</v>
       </c>
       <c r="E78">
-        <v>2323.784</v>
+        <v>2378.817999999999</v>
       </c>
       <c r="F78">
-        <v>4182.584</v>
+        <v>4237.617999999999</v>
       </c>
       <c r="G78">
         <v>275.2</v>
@@ -7689,28 +7689,28 @@
         <v>681.7</v>
       </c>
       <c r="M78">
-        <v>317.0398672</v>
+        <v>321.2114444</v>
       </c>
       <c r="N78">
-        <v>364.6601328</v>
+        <v>360.4885556</v>
       </c>
       <c r="O78">
-        <v>91.16503320000001</v>
+        <v>90.12213890000001</v>
       </c>
       <c r="P78">
-        <v>273.4950996</v>
+        <v>270.3664167000001</v>
       </c>
       <c r="Q78">
-        <v>599.3950996</v>
+        <v>596.2664167</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2429786537817624</v>
+        <v>0.2509166028067931</v>
       </c>
       <c r="T78">
-        <v>2.714238388333746</v>
+        <v>2.82350724454686</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.150202767937571</v>
+        <v>2.122278056665655</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1014853186455624</v>
+        <v>0.1014497603835018</v>
       </c>
       <c r="C79">
-        <v>1440.234987473019</v>
+        <v>1388.653094893193</v>
       </c>
       <c r="D79">
-        <v>5402.652987473019</v>
+        <v>5406.105094893193</v>
       </c>
       <c r="E79">
-        <v>2378.817999999999</v>
+        <v>2433.852</v>
       </c>
       <c r="F79">
-        <v>4237.617999999999</v>
+        <v>4292.652</v>
       </c>
       <c r="G79">
         <v>275.2</v>
@@ -7771,28 +7771,28 @@
         <v>681.7</v>
       </c>
       <c r="M79">
-        <v>321.2114444</v>
+        <v>325.3830216</v>
       </c>
       <c r="N79">
-        <v>360.4885556</v>
+        <v>356.3169784</v>
       </c>
       <c r="O79">
-        <v>90.12213890000001</v>
+        <v>89.07924460000001</v>
       </c>
       <c r="P79">
-        <v>270.3664167000001</v>
+        <v>267.2377338</v>
       </c>
       <c r="Q79">
-        <v>596.2664167</v>
+        <v>593.1377338</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2509166028067931</v>
+        <v>0.259576183561372</v>
       </c>
       <c r="T79">
-        <v>2.82350724454686</v>
+        <v>2.942709633142985</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.122278056665655</v>
+        <v>2.09506936363148</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1014497603835018</v>
+        <v>0.1014142021214413</v>
       </c>
       <c r="C80">
-        <v>1388.653094893193</v>
+        <v>1337.075616687237</v>
       </c>
       <c r="D80">
-        <v>5406.105094893193</v>
+        <v>5409.561616687237</v>
       </c>
       <c r="E80">
-        <v>2433.852</v>
+        <v>2488.886</v>
       </c>
       <c r="F80">
-        <v>4292.652</v>
+        <v>4347.686</v>
       </c>
       <c r="G80">
         <v>275.2</v>
@@ -7853,28 +7853,28 @@
         <v>681.7</v>
       </c>
       <c r="M80">
-        <v>325.3830216</v>
+        <v>329.5545988</v>
       </c>
       <c r="N80">
-        <v>356.3169784</v>
+        <v>352.1454012</v>
       </c>
       <c r="O80">
-        <v>89.07924460000001</v>
+        <v>88.03635030000001</v>
       </c>
       <c r="P80">
-        <v>267.2377338</v>
+        <v>264.1090509000001</v>
       </c>
       <c r="Q80">
-        <v>593.1377338</v>
+        <v>590.0090509</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.259576183561372</v>
+        <v>0.2690604862925776</v>
       </c>
       <c r="T80">
-        <v>2.942709633142985</v>
+        <v>3.073264630176835</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.09506936363148</v>
+        <v>2.068549498269056</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1014142021214413</v>
+        <v>0.1013786438593807</v>
       </c>
       <c r="C81">
-        <v>1337.075616687237</v>
+        <v>1285.502561327871</v>
       </c>
       <c r="D81">
-        <v>5409.561616687237</v>
+        <v>5413.022561327872</v>
       </c>
       <c r="E81">
-        <v>2488.886</v>
+        <v>2543.92</v>
       </c>
       <c r="F81">
-        <v>4347.686</v>
+        <v>4402.72</v>
       </c>
       <c r="G81">
         <v>275.2</v>
@@ -7935,28 +7935,28 @@
         <v>681.7</v>
       </c>
       <c r="M81">
-        <v>329.5545988</v>
+        <v>333.7261760000001</v>
       </c>
       <c r="N81">
-        <v>352.1454012</v>
+        <v>347.973824</v>
       </c>
       <c r="O81">
-        <v>88.03635030000001</v>
+        <v>86.99345599999999</v>
       </c>
       <c r="P81">
-        <v>264.1090509000001</v>
+        <v>260.980368</v>
       </c>
       <c r="Q81">
-        <v>590.0090509</v>
+        <v>586.880368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2690604862925776</v>
+        <v>0.2794932192969036</v>
       </c>
       <c r="T81">
-        <v>3.073264630176835</v>
+        <v>3.216875126914071</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.068549498269056</v>
+        <v>2.042692629540692</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1013786438593807</v>
+        <v>0.1013430855973202</v>
       </c>
       <c r="C82">
-        <v>1285.502561327871</v>
+        <v>1233.933937309519</v>
       </c>
       <c r="D82">
-        <v>5413.022561327872</v>
+        <v>5416.487937309519</v>
       </c>
       <c r="E82">
-        <v>2543.92</v>
+        <v>2598.954</v>
       </c>
       <c r="F82">
-        <v>4402.72</v>
+        <v>4457.754</v>
       </c>
       <c r="G82">
         <v>275.2</v>
@@ -8017,28 +8017,28 @@
         <v>681.7</v>
       </c>
       <c r="M82">
-        <v>333.7261760000001</v>
+        <v>337.8977532</v>
       </c>
       <c r="N82">
-        <v>347.973824</v>
+        <v>343.8022468</v>
       </c>
       <c r="O82">
-        <v>86.99345599999999</v>
+        <v>85.95056170000001</v>
       </c>
       <c r="P82">
-        <v>260.980368</v>
+        <v>257.8516851000001</v>
       </c>
       <c r="Q82">
-        <v>586.880368</v>
+        <v>583.7516851</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2794932192969036</v>
+        <v>0.2910241347227377</v>
       </c>
       <c r="T82">
-        <v>3.216875126914071</v>
+        <v>3.375602518044699</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.042692629540692</v>
+        <v>2.017474202015499</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1013430855973202</v>
+        <v>0.1100405273352596</v>
       </c>
       <c r="C83">
-        <v>1233.933937309519</v>
+        <v>445.5686554359272</v>
       </c>
       <c r="D83">
-        <v>5416.487937309519</v>
+        <v>4683.156655435928</v>
       </c>
       <c r="E83">
-        <v>2598.954</v>
+        <v>2653.988</v>
       </c>
       <c r="F83">
-        <v>4457.754</v>
+        <v>4512.788</v>
       </c>
       <c r="G83">
         <v>275.2</v>
@@ -8099,45 +8099,45 @@
         <v>681.7</v>
       </c>
       <c r="M83">
-        <v>337.8977532</v>
+        <v>406.15092</v>
       </c>
       <c r="N83">
-        <v>343.8022468</v>
+        <v>275.54908</v>
       </c>
       <c r="O83">
-        <v>85.95056170000001</v>
+        <v>68.88727</v>
       </c>
       <c r="P83">
-        <v>257.8516851000001</v>
+        <v>206.66181</v>
       </c>
       <c r="Q83">
-        <v>583.7516851</v>
+        <v>532.5618099999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2910241347227377</v>
+        <v>0.3038362629736645</v>
       </c>
       <c r="T83">
-        <v>3.375602518044699</v>
+        <v>3.55196628596762</v>
       </c>
       <c r="U83">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.017474202015499</v>
+        <v>1.678440122701187</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1100405273352596</v>
+        <v>0.110111469073199</v>
       </c>
       <c r="C84">
-        <v>445.5686554359272</v>
+        <v>385.3686830679035</v>
       </c>
       <c r="D84">
-        <v>4683.156655435928</v>
+        <v>4677.990683067904</v>
       </c>
       <c r="E84">
-        <v>2653.988</v>
+        <v>2709.022</v>
       </c>
       <c r="F84">
-        <v>4512.788</v>
+        <v>4567.822</v>
       </c>
       <c r="G84">
         <v>275.2</v>
@@ -8181,28 +8181,28 @@
         <v>681.7</v>
       </c>
       <c r="M84">
-        <v>406.15092</v>
+        <v>411.10398</v>
       </c>
       <c r="N84">
-        <v>275.54908</v>
+        <v>270.5960200000001</v>
       </c>
       <c r="O84">
-        <v>68.88727</v>
+        <v>67.64900500000002</v>
       </c>
       <c r="P84">
-        <v>206.66181</v>
+        <v>202.9470150000001</v>
       </c>
       <c r="Q84">
-        <v>532.5618099999999</v>
+        <v>528.8470150000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3038362629736645</v>
+        <v>0.3181557004305826</v>
       </c>
       <c r="T84">
-        <v>3.55196628596762</v>
+        <v>3.749078732469708</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.678440122701187</v>
+        <v>1.658217952548161</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.110111469073199</v>
+        <v>0.1101824108111385</v>
       </c>
       <c r="C85">
-        <v>385.3686830679035</v>
+        <v>325.1800952707054</v>
       </c>
       <c r="D85">
-        <v>4677.990683067904</v>
+        <v>4672.836095270705</v>
       </c>
       <c r="E85">
-        <v>2709.022</v>
+        <v>2764.056</v>
       </c>
       <c r="F85">
-        <v>4567.822</v>
+        <v>4622.856</v>
       </c>
       <c r="G85">
         <v>275.2</v>
@@ -8263,28 +8263,28 @@
         <v>681.7</v>
       </c>
       <c r="M85">
-        <v>411.10398</v>
+        <v>416.05704</v>
       </c>
       <c r="N85">
-        <v>270.5960200000001</v>
+        <v>265.6429600000001</v>
       </c>
       <c r="O85">
-        <v>67.64900500000002</v>
+        <v>66.41074000000002</v>
       </c>
       <c r="P85">
-        <v>202.9470150000001</v>
+        <v>199.23222</v>
       </c>
       <c r="Q85">
-        <v>528.8470150000001</v>
+        <v>525.13222</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3181557004305826</v>
+        <v>0.3342650675696155</v>
       </c>
       <c r="T85">
-        <v>3.749078732469708</v>
+        <v>3.970830234784557</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.658217952548161</v>
+        <v>1.638477262636873</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1101824108111385</v>
+        <v>0.1102533525490779</v>
       </c>
       <c r="C86">
-        <v>325.1800952707044</v>
+        <v>265.0028544524375</v>
       </c>
       <c r="D86">
-        <v>4672.836095270704</v>
+        <v>4667.692854452437</v>
       </c>
       <c r="E86">
-        <v>2764.056</v>
+        <v>2819.089999999999</v>
       </c>
       <c r="F86">
-        <v>4622.856</v>
+        <v>4677.889999999999</v>
       </c>
       <c r="G86">
         <v>275.2</v>
@@ -8345,28 +8345,28 @@
         <v>681.7</v>
       </c>
       <c r="M86">
-        <v>416.05704</v>
+        <v>421.0100999999999</v>
       </c>
       <c r="N86">
-        <v>265.6429600000001</v>
+        <v>260.6899000000001</v>
       </c>
       <c r="O86">
-        <v>66.41074000000002</v>
+        <v>65.17247500000003</v>
       </c>
       <c r="P86">
-        <v>199.23222</v>
+        <v>195.5174250000001</v>
       </c>
       <c r="Q86">
-        <v>525.13222</v>
+        <v>521.4174250000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3342650675696153</v>
+        <v>0.3525223503271859</v>
       </c>
       <c r="T86">
-        <v>3.970830234784554</v>
+        <v>4.222148604074716</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.638477262636873</v>
+        <v>1.619201059547028</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1102533525490779</v>
+        <v>0.1103242942870173</v>
       </c>
       <c r="C87">
-        <v>265.0028544524375</v>
+        <v>204.8369231865272</v>
       </c>
       <c r="D87">
-        <v>4667.692854452437</v>
+        <v>4662.560923186527</v>
       </c>
       <c r="E87">
-        <v>2819.089999999999</v>
+        <v>2874.124</v>
       </c>
       <c r="F87">
-        <v>4677.889999999999</v>
+        <v>4732.924</v>
       </c>
       <c r="G87">
         <v>275.2</v>
@@ -8427,28 +8427,28 @@
         <v>681.7</v>
       </c>
       <c r="M87">
-        <v>421.0100999999999</v>
+        <v>425.96316</v>
       </c>
       <c r="N87">
-        <v>260.6899000000001</v>
+        <v>255.7368400000001</v>
       </c>
       <c r="O87">
-        <v>65.17247500000003</v>
+        <v>63.93421000000002</v>
       </c>
       <c r="P87">
-        <v>195.5174250000001</v>
+        <v>191.8026300000001</v>
       </c>
       <c r="Q87">
-        <v>521.4174250000001</v>
+        <v>517.70263</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3525223503271859</v>
+        <v>0.373387816335838</v>
       </c>
       <c r="T87">
-        <v>4.222148604074716</v>
+        <v>4.509369597549187</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.619201059547028</v>
+        <v>1.600373140249969</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1103242942870173</v>
+        <v>0.1103952360249568</v>
       </c>
       <c r="C88">
-        <v>204.8369231865272</v>
+        <v>144.6822642108164</v>
       </c>
       <c r="D88">
-        <v>4662.560923186527</v>
+        <v>4657.440264210816</v>
       </c>
       <c r="E88">
-        <v>2874.124</v>
+        <v>2929.157999999999</v>
       </c>
       <c r="F88">
-        <v>4732.924</v>
+        <v>4787.958</v>
       </c>
       <c r="G88">
         <v>275.2</v>
@@ -8509,28 +8509,28 @@
         <v>681.7</v>
       </c>
       <c r="M88">
-        <v>425.96316</v>
+        <v>430.91622</v>
       </c>
       <c r="N88">
-        <v>255.7368400000001</v>
+        <v>250.7837800000001</v>
       </c>
       <c r="O88">
-        <v>63.93421000000002</v>
+        <v>62.69594500000002</v>
       </c>
       <c r="P88">
-        <v>191.8026300000001</v>
+        <v>188.0878350000001</v>
       </c>
       <c r="Q88">
-        <v>517.70263</v>
+        <v>513.987835</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.373387816335838</v>
+        <v>0.3974633540381289</v>
       </c>
       <c r="T88">
-        <v>4.509369597549187</v>
+        <v>4.840778436173576</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.600373140249969</v>
+        <v>1.581978046683878</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1103952360249568</v>
+        <v>0.1104661777628962</v>
       </c>
       <c r="C89">
-        <v>144.6822642108164</v>
+        <v>84.53884042666141</v>
       </c>
       <c r="D89">
-        <v>4657.440264210816</v>
+        <v>4652.330840426661</v>
       </c>
       <c r="E89">
-        <v>2929.157999999999</v>
+        <v>2984.191999999999</v>
       </c>
       <c r="F89">
-        <v>4787.958</v>
+        <v>4842.991999999999</v>
       </c>
       <c r="G89">
         <v>275.2</v>
@@ -8591,28 +8591,28 @@
         <v>681.7</v>
       </c>
       <c r="M89">
-        <v>430.91622</v>
+        <v>435.8692799999999</v>
       </c>
       <c r="N89">
-        <v>250.7837800000001</v>
+        <v>245.8307200000001</v>
       </c>
       <c r="O89">
-        <v>62.69594500000002</v>
+        <v>61.45768000000002</v>
       </c>
       <c r="P89">
-        <v>188.0878350000001</v>
+        <v>184.3730400000001</v>
       </c>
       <c r="Q89">
-        <v>513.987835</v>
+        <v>510.27304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3974633540381289</v>
+        <v>0.4255514813574683</v>
       </c>
       <c r="T89">
-        <v>4.840778436173576</v>
+        <v>5.227422081235363</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.581978046683878</v>
+        <v>1.564001023426106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1104661777628962</v>
+        <v>0.1105371195008356</v>
       </c>
       <c r="C90">
-        <v>84.53884042666141</v>
+        <v>24.40661489803006</v>
       </c>
       <c r="D90">
-        <v>4652.330840426661</v>
+        <v>4647.23261489803</v>
       </c>
       <c r="E90">
-        <v>2984.191999999999</v>
+        <v>3039.226</v>
       </c>
       <c r="F90">
-        <v>4842.991999999999</v>
+        <v>4898.026</v>
       </c>
       <c r="G90">
         <v>275.2</v>
@@ -8673,28 +8673,28 @@
         <v>681.7</v>
       </c>
       <c r="M90">
-        <v>435.8692799999999</v>
+        <v>440.82234</v>
       </c>
       <c r="N90">
-        <v>245.8307200000001</v>
+        <v>240.87766</v>
       </c>
       <c r="O90">
-        <v>61.45768000000002</v>
+        <v>60.21941500000001</v>
       </c>
       <c r="P90">
-        <v>184.3730400000001</v>
+        <v>180.658245</v>
       </c>
       <c r="Q90">
-        <v>510.27304</v>
+        <v>506.558245</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4255514813574683</v>
+        <v>0.4587465409166876</v>
       </c>
       <c r="T90">
-        <v>5.227422081235363</v>
+        <v>5.684364570853839</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.564001023426106</v>
+        <v>1.546427978219071</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1105371195008356</v>
+        <v>0.1106080612387751</v>
       </c>
       <c r="C91">
-        <v>24.40661489803006</v>
+        <v>-35.71444914937365</v>
       </c>
       <c r="D91">
-        <v>4647.23261489803</v>
+        <v>4642.145550850626</v>
       </c>
       <c r="E91">
-        <v>3039.226</v>
+        <v>3094.259999999999</v>
       </c>
       <c r="F91">
-        <v>4898.026</v>
+        <v>4953.059999999999</v>
       </c>
       <c r="G91">
         <v>275.2</v>
@@ -8755,28 +8755,28 @@
         <v>681.7</v>
       </c>
       <c r="M91">
-        <v>440.82234</v>
+        <v>445.7753999999999</v>
       </c>
       <c r="N91">
-        <v>240.87766</v>
+        <v>235.9246000000001</v>
       </c>
       <c r="O91">
-        <v>60.21941500000001</v>
+        <v>58.98115000000003</v>
       </c>
       <c r="P91">
-        <v>180.658245</v>
+        <v>176.9434500000001</v>
       </c>
       <c r="Q91">
-        <v>506.558245</v>
+        <v>502.8434500000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4587465409166876</v>
+        <v>0.4985806123877508</v>
       </c>
       <c r="T91">
-        <v>5.684364570853839</v>
+        <v>6.232695558396012</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.546427978219071</v>
+        <v>1.529245445127748</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1106080612387751</v>
+        <v>0.1106790029767145</v>
       </c>
       <c r="C92">
-        <v>-35.71444914937365</v>
+        <v>-95.8243883290088</v>
       </c>
       <c r="D92">
-        <v>4642.145550850626</v>
+        <v>4637.069611670991</v>
       </c>
       <c r="E92">
-        <v>3094.259999999999</v>
+        <v>3149.294</v>
       </c>
       <c r="F92">
-        <v>4953.059999999999</v>
+        <v>5008.094</v>
       </c>
       <c r="G92">
         <v>275.2</v>
@@ -8837,28 +8837,28 @@
         <v>681.7</v>
       </c>
       <c r="M92">
-        <v>445.7753999999999</v>
+        <v>450.72846</v>
       </c>
       <c r="N92">
-        <v>235.9246000000001</v>
+        <v>230.9715400000001</v>
       </c>
       <c r="O92">
-        <v>58.98115000000003</v>
+        <v>57.74288500000002</v>
       </c>
       <c r="P92">
-        <v>176.9434500000001</v>
+        <v>173.2286550000001</v>
       </c>
       <c r="Q92">
-        <v>502.8434500000001</v>
+        <v>499.128655</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4985806123877508</v>
+        <v>0.5472666997412724</v>
       </c>
       <c r="T92">
-        <v>6.232695558396012</v>
+        <v>6.90287787650311</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.529245445127748</v>
+        <v>1.512440550126344</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1106790029767145</v>
+        <v>0.1538517838176568</v>
       </c>
       <c r="C93">
-        <v>-95.8243883290088</v>
+        <v>-2003.629189657982</v>
       </c>
       <c r="D93">
-        <v>4637.069611670991</v>
+        <v>2784.298810342018</v>
       </c>
       <c r="E93">
-        <v>3149.294</v>
+        <v>3204.328</v>
       </c>
       <c r="F93">
-        <v>5008.094</v>
+        <v>5063.128</v>
       </c>
       <c r="G93">
         <v>275.2</v>
@@ -8919,45 +8919,45 @@
         <v>681.7</v>
       </c>
       <c r="M93">
-        <v>450.72846</v>
+        <v>743.2671904</v>
       </c>
       <c r="N93">
-        <v>230.9715400000001</v>
+        <v>-61.56719039999996</v>
       </c>
       <c r="O93">
-        <v>57.74288500000002</v>
+        <v>-15.39179759999999</v>
       </c>
       <c r="P93">
-        <v>173.2286550000001</v>
+        <v>-46.17539279999997</v>
       </c>
       <c r="Q93">
-        <v>499.128655</v>
+        <v>279.7246072</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5472666997412724</v>
+        <v>0.6220375510186713</v>
       </c>
       <c r="T93">
-        <v>6.90287787650311</v>
+        <v>7.932126788457496</v>
       </c>
       <c r="U93">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.25</v>
+        <v>0.2292917031737716</v>
       </c>
       <c r="W93">
-        <v>0.0675</v>
+        <v>0.1131399779740903</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.512440550126344</v>
+        <v>0.9171668126950866</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1538517838176568</v>
+        <v>0.1548617838176568</v>
       </c>
       <c r="C94">
-        <v>-2003.629189657982</v>
+        <v>-2084.448040226237</v>
       </c>
       <c r="D94">
-        <v>2784.298810342018</v>
+        <v>2758.513959773763</v>
       </c>
       <c r="E94">
-        <v>3204.328</v>
+        <v>3259.362</v>
       </c>
       <c r="F94">
-        <v>5063.128</v>
+        <v>5118.162</v>
       </c>
       <c r="G94">
         <v>275.2</v>
@@ -9001,37 +9001,37 @@
         <v>681.7</v>
       </c>
       <c r="M94">
-        <v>743.2671904</v>
+        <v>751.3461816000001</v>
       </c>
       <c r="N94">
-        <v>-61.56719039999996</v>
+        <v>-69.64618160000009</v>
       </c>
       <c r="O94">
-        <v>-15.39179759999999</v>
+        <v>-17.41154540000002</v>
       </c>
       <c r="P94">
-        <v>-46.17539279999997</v>
+        <v>-52.23463620000007</v>
       </c>
       <c r="Q94">
-        <v>279.7246072</v>
+        <v>273.6653637999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6220375510186713</v>
+        <v>0.7043572011641961</v>
       </c>
       <c r="T94">
-        <v>7.932126788457496</v>
+        <v>9.065287758237142</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2292917031737716</v>
+        <v>0.2268262009891074</v>
       </c>
       <c r="W94">
-        <v>0.1131399779740903</v>
+        <v>0.1135019136947991</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9171668126950866</v>
+        <v>0.9073048039564295</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1548617838176568</v>
+        <v>0.1558717838176568</v>
       </c>
       <c r="C95">
-        <v>-2084.448040226237</v>
+        <v>-2164.793695972516</v>
       </c>
       <c r="D95">
-        <v>2758.513959773763</v>
+        <v>2733.202304027484</v>
       </c>
       <c r="E95">
-        <v>3259.362</v>
+        <v>3314.396</v>
       </c>
       <c r="F95">
-        <v>5118.162</v>
+        <v>5173.196</v>
       </c>
       <c r="G95">
         <v>275.2</v>
@@ -9083,37 +9083,37 @@
         <v>681.7</v>
       </c>
       <c r="M95">
-        <v>751.3461816000001</v>
+        <v>759.4251728</v>
       </c>
       <c r="N95">
-        <v>-69.64618160000009</v>
+        <v>-77.7251728</v>
       </c>
       <c r="O95">
-        <v>-17.41154540000002</v>
+        <v>-19.4312932</v>
       </c>
       <c r="P95">
-        <v>-52.23463620000007</v>
+        <v>-58.2938796</v>
       </c>
       <c r="Q95">
-        <v>273.6653637999999</v>
+        <v>267.6061204</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7043572011641961</v>
+        <v>0.8141167346915621</v>
       </c>
       <c r="T95">
-        <v>9.065287758237142</v>
+        <v>10.57616905127667</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2268262009891074</v>
+        <v>0.2244131562977339</v>
       </c>
       <c r="W95">
-        <v>0.1135019136947991</v>
+        <v>0.1138561486554927</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9073048039564295</v>
+        <v>0.8976526251909357</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1558717838176568</v>
+        <v>0.1568817838176568</v>
       </c>
       <c r="C96">
-        <v>-2164.793695972516</v>
+        <v>-2244.679064326479</v>
       </c>
       <c r="D96">
-        <v>2733.202304027484</v>
+        <v>2708.350935673521</v>
       </c>
       <c r="E96">
-        <v>3314.396</v>
+        <v>3369.43</v>
       </c>
       <c r="F96">
-        <v>5173.196</v>
+        <v>5228.23</v>
       </c>
       <c r="G96">
         <v>275.2</v>
@@ -9165,37 +9165,37 @@
         <v>681.7</v>
       </c>
       <c r="M96">
-        <v>759.4251728</v>
+        <v>767.5041640000002</v>
       </c>
       <c r="N96">
-        <v>-77.7251728</v>
+        <v>-85.80416400000013</v>
       </c>
       <c r="O96">
-        <v>-19.4312932</v>
+        <v>-21.45104100000003</v>
       </c>
       <c r="P96">
-        <v>-58.2938796</v>
+        <v>-64.3531230000001</v>
       </c>
       <c r="Q96">
-        <v>267.6061204</v>
+        <v>261.5468769999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8141167346915621</v>
+        <v>0.9677800816298751</v>
       </c>
       <c r="T96">
-        <v>10.57616905127667</v>
+        <v>12.69140286153201</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2244131562977339</v>
+        <v>0.2220509125472314</v>
       </c>
       <c r="W96">
-        <v>0.1138561486554927</v>
+        <v>0.1142029260380664</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8976526251909357</v>
+        <v>0.8882036501889258</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1568817838176568</v>
+        <v>0.1578917838176568</v>
       </c>
       <c r="C97">
-        <v>-2244.679064326479</v>
+        <v>-2324.116587509588</v>
       </c>
       <c r="D97">
-        <v>2708.350935673521</v>
+        <v>2683.947412490412</v>
       </c>
       <c r="E97">
-        <v>3369.43</v>
+        <v>3424.464</v>
       </c>
       <c r="F97">
-        <v>5228.23</v>
+        <v>5283.264</v>
       </c>
       <c r="G97">
         <v>275.2</v>
@@ -9247,37 +9247,37 @@
         <v>681.7</v>
       </c>
       <c r="M97">
-        <v>767.5041640000002</v>
+        <v>775.5831552000001</v>
       </c>
       <c r="N97">
-        <v>-85.80416400000013</v>
+        <v>-93.88315520000003</v>
       </c>
       <c r="O97">
-        <v>-21.45104100000003</v>
+        <v>-23.47078880000001</v>
       </c>
       <c r="P97">
-        <v>-64.3531230000001</v>
+        <v>-70.41236640000002</v>
       </c>
       <c r="Q97">
-        <v>261.5468769999999</v>
+        <v>255.4876336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9677800816298751</v>
+        <v>1.198275102037344</v>
       </c>
       <c r="T97">
-        <v>12.69140286153201</v>
+        <v>15.86425357691502</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2220509125472314</v>
+        <v>0.2197378822081978</v>
       </c>
       <c r="W97">
-        <v>0.1142029260380664</v>
+        <v>0.1145424788918366</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8882036501889258</v>
+        <v>0.8789515288327912</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1578917838176568</v>
+        <v>0.1589017838176568</v>
       </c>
       <c r="C98">
-        <v>-2324.116587509587</v>
+        <v>-2403.118263306688</v>
       </c>
       <c r="D98">
-        <v>2683.947412490413</v>
+        <v>2659.979736693312</v>
       </c>
       <c r="E98">
-        <v>3424.463999999999</v>
+        <v>3479.498</v>
       </c>
       <c r="F98">
-        <v>5283.263999999999</v>
+        <v>5338.298</v>
       </c>
       <c r="G98">
         <v>275.2</v>
@@ -9329,37 +9329,37 @@
         <v>681.7</v>
       </c>
       <c r="M98">
-        <v>775.5831552</v>
+        <v>783.6621464000001</v>
       </c>
       <c r="N98">
-        <v>-93.88315519999992</v>
+        <v>-101.9621464000001</v>
       </c>
       <c r="O98">
-        <v>-23.47078879999998</v>
+        <v>-25.49053660000001</v>
       </c>
       <c r="P98">
-        <v>-70.41236639999994</v>
+        <v>-76.47160980000004</v>
       </c>
       <c r="Q98">
-        <v>255.4876336</v>
+        <v>249.4283901999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.198275102037341</v>
+        <v>1.582433469383122</v>
       </c>
       <c r="T98">
-        <v>15.86425357691497</v>
+        <v>21.1523381025533</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2197378822081978</v>
+        <v>0.2174725432163607</v>
       </c>
       <c r="W98">
-        <v>0.1145424788918366</v>
+        <v>0.1148750306558383</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8789515288327914</v>
+        <v>0.8698901728654428</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1589017838176568</v>
+        <v>0.1599117838176568</v>
       </c>
       <c r="C99">
-        <v>-2403.118263306688</v>
+        <v>-2481.695664734478</v>
       </c>
       <c r="D99">
-        <v>2659.979736693312</v>
+        <v>2636.436335265522</v>
       </c>
       <c r="E99">
-        <v>3479.498</v>
+        <v>3534.531999999999</v>
       </c>
       <c r="F99">
-        <v>5338.298</v>
+        <v>5393.331999999999</v>
       </c>
       <c r="G99">
         <v>275.2</v>
@@ -9411,37 +9411,37 @@
         <v>681.7</v>
       </c>
       <c r="M99">
-        <v>783.6621464000001</v>
+        <v>791.7411376</v>
       </c>
       <c r="N99">
-        <v>-101.9621464000001</v>
+        <v>-110.0411376</v>
       </c>
       <c r="O99">
-        <v>-25.49053660000001</v>
+        <v>-27.51028439999999</v>
       </c>
       <c r="P99">
-        <v>-76.47160980000004</v>
+        <v>-82.53085319999997</v>
       </c>
       <c r="Q99">
-        <v>249.4283901999999</v>
+        <v>243.3691468</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.582433469383122</v>
+        <v>2.350750204074682</v>
       </c>
       <c r="T99">
-        <v>21.1523381025533</v>
+        <v>31.72850715382994</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2174725432163607</v>
+        <v>0.2152534356325203</v>
       </c>
       <c r="W99">
-        <v>0.1148750306558383</v>
+        <v>0.115200795649146</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8698901728654428</v>
+        <v>0.8610137425300812</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1599117838176568</v>
+        <v>0.1609217838176568</v>
       </c>
       <c r="C100">
-        <v>-2481.695664734478</v>
+        <v>-2559.85995867464</v>
       </c>
       <c r="D100">
-        <v>2636.436335265522</v>
+        <v>2613.306041325361</v>
       </c>
       <c r="E100">
-        <v>3534.531999999999</v>
+        <v>3589.566</v>
       </c>
       <c r="F100">
-        <v>5393.331999999999</v>
+        <v>5448.366</v>
       </c>
       <c r="G100">
         <v>275.2</v>
@@ -9493,37 +9493,37 @@
         <v>681.7</v>
       </c>
       <c r="M100">
-        <v>791.7411376</v>
+        <v>799.8201288</v>
       </c>
       <c r="N100">
-        <v>-110.0411376</v>
+        <v>-118.1201288</v>
       </c>
       <c r="O100">
-        <v>-27.51028439999999</v>
+        <v>-29.53003219999999</v>
       </c>
       <c r="P100">
-        <v>-82.53085319999997</v>
+        <v>-88.59009659999998</v>
       </c>
       <c r="Q100">
-        <v>243.3691468</v>
+        <v>237.3099034</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.350750204074682</v>
+        <v>4.655700408149364</v>
       </c>
       <c r="T100">
-        <v>31.72850715382994</v>
+        <v>63.45701430765989</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2152534356325203</v>
+        <v>0.2130791585049191</v>
       </c>
       <c r="W100">
-        <v>0.115200795649146</v>
+        <v>0.1155199795314779</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8610137425300812</v>
+        <v>0.8523166340196764</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1609217838176568</v>
-      </c>
-      <c r="C101">
-        <v>-2559.85995867464</v>
-      </c>
-      <c r="D101">
-        <v>2613.306041325361</v>
-      </c>
-      <c r="E101">
-        <v>3589.566</v>
-      </c>
-      <c r="F101">
-        <v>5448.366</v>
-      </c>
-      <c r="G101">
-        <v>275.2</v>
-      </c>
-      <c r="H101">
-        <v>3644.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1007.6</v>
-      </c>
-      <c r="K101">
-        <v>325.9</v>
-      </c>
-      <c r="L101">
-        <v>681.7</v>
-      </c>
-      <c r="M101">
-        <v>799.8201288</v>
-      </c>
-      <c r="N101">
-        <v>-118.1201288</v>
-      </c>
-      <c r="O101">
-        <v>-29.53003219999999</v>
-      </c>
-      <c r="P101">
-        <v>-88.59009659999998</v>
-      </c>
-      <c r="Q101">
-        <v>237.3099034</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.655700408149364</v>
-      </c>
-      <c r="T101">
-        <v>63.45701430765989</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2130791585049191</v>
-      </c>
-      <c r="W101">
-        <v>0.1155199795314779</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8523166340196764</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
